--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="52">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -110,10 +110,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>EngineId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Resource</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -171,6 +167,54 @@
   </si>
   <si>
     <t>engine_test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone_miner2</t>
+  </si>
+  <si>
+    <t>stone_miner3</t>
+  </si>
+  <si>
+    <t>stone_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone_processor2</t>
+  </si>
+  <si>
+    <t>stone_processor3</t>
+  </si>
+  <si>
+    <t>돌 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>돌 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>돌 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>돌 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>Facility</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -239,14 +283,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F15" totalsRowShown="0">
-  <autoFilter ref="A1:F15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F21" totalsRowShown="0">
+  <autoFilter ref="A1:F21"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="4" name="Name"/>
     <tableColumn id="2" name="DisplayName"/>
     <tableColumn id="5" name="ItemType"/>
-    <tableColumn id="6" name="EngineId"/>
+    <tableColumn id="6" name="UnitId"/>
     <tableColumn id="3" name="ItemIcon"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -516,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.875" customWidth="1"/>
@@ -539,7 +583,7 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -556,10 +600,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -573,10 +617,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -590,10 +634,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -607,10 +651,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -624,10 +668,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -641,10 +685,10 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -658,10 +702,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -675,10 +719,10 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -686,19 +730,19 @@
         <v>1101</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10">
         <v>201001</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -706,19 +750,19 @@
         <v>1102</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>201002</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -726,19 +770,19 @@
         <v>1103</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>201003</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -746,19 +790,19 @@
         <v>1104</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>202001</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -766,19 +810,19 @@
         <v>1105</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14">
         <v>202002</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -786,19 +830,139 @@
         <v>1106</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
         <v>34</v>
-      </c>
-      <c r="D15" t="s">
-        <v>35</v>
       </c>
       <c r="E15">
         <v>202003</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1201</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16">
+        <v>101011</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1202</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17">
+        <v>101012</v>
+      </c>
+      <c r="F17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1203</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18">
+        <v>101013</v>
+      </c>
+      <c r="F18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1204</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19">
+        <v>101021</v>
+      </c>
+      <c r="F19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1205</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20">
+        <v>101022</v>
+      </c>
+      <c r="F20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1206</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21">
+        <v>101023</v>
+      </c>
+      <c r="F21" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="74">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -215,6 +215,78 @@
   </si>
   <si>
     <t>Facility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lab1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구소 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구소 Lv.2</t>
+  </si>
+  <si>
+    <t>연구소 Lv.3</t>
+  </si>
+  <si>
+    <t>연구소 Lv.4</t>
+  </si>
+  <si>
+    <t>연구소 Lv.5</t>
+  </si>
+  <si>
+    <t>lab2</t>
+  </si>
+  <si>
+    <t>lab3</t>
+  </si>
+  <si>
+    <t>lab4</t>
+  </si>
+  <si>
+    <t>lab5</t>
+  </si>
+  <si>
+    <t>engineMerger1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMerger2</t>
+  </si>
+  <si>
+    <t>engineMerger3</t>
+  </si>
+  <si>
+    <t>engineMerger4</t>
+  </si>
+  <si>
+    <t>engineMerger5</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>labIcon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMergerIcon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -283,8 +355,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F21" totalsRowShown="0">
-  <autoFilter ref="A1:F21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F31" totalsRowShown="0">
+  <autoFilter ref="A1:F31"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="4" name="Name"/>
@@ -560,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.875" customWidth="1"/>
@@ -965,6 +1037,206 @@
         <v>37</v>
       </c>
     </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1301</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22">
+        <v>110001</v>
+      </c>
+      <c r="F22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1302</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23">
+        <v>110002</v>
+      </c>
+      <c r="F23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>1303</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24">
+        <v>110003</v>
+      </c>
+      <c r="F24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1304</v>
+      </c>
+      <c r="B25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25">
+        <v>110004</v>
+      </c>
+      <c r="F25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1305</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26">
+        <v>110005</v>
+      </c>
+      <c r="F26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1401</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27">
+        <v>111001</v>
+      </c>
+      <c r="F27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>1402</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28">
+        <v>111002</v>
+      </c>
+      <c r="F28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1403</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29">
+        <v>111003</v>
+      </c>
+      <c r="F29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1404</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30">
+        <v>111004</v>
+      </c>
+      <c r="F30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>1405</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31">
+        <v>111005</v>
+      </c>
+      <c r="F31" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmung\Desktop\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B676EC1B-D469-46E1-9B79-299A31514629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16170" windowHeight="9705"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="6189" windowHeight="14794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,13 +288,61 @@
   </si>
   <si>
     <t>engineMergerIcon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obsidian_Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obsidian_Resource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tunstein_Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tunstein_Resource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Titanium_Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Titanium_Resource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옵시디언 광물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옵시디언 자재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 광물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 자재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 광물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 자재</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -311,20 +360,63 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -333,8 +425,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -355,15 +465,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F31" totalsRowShown="0">
-  <autoFilter ref="A1:F31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:F37" totalsRowShown="0">
+  <autoFilter ref="A1:F37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="4" name="Name"/>
-    <tableColumn id="2" name="DisplayName"/>
-    <tableColumn id="5" name="ItemType"/>
-    <tableColumn id="6" name="UnitId"/>
-    <tableColumn id="3" name="ItemIcon"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ItemType"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="UnitId"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ItemIcon"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -631,17 +741,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="17.875" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
-    <col min="4" max="5" width="17.875" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -661,7 +771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -678,7 +788,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -695,7 +805,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -712,7 +822,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -729,7 +839,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -746,7 +856,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -763,7 +873,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -780,7 +890,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -797,443 +907,545 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>1010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>1011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>1012</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>1013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>1014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4">
         <v>1101</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E10">
+      <c r="E16" s="5">
         <v>201001</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F16" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1">
         <v>1102</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E11">
+      <c r="E17" s="2">
         <v>201002</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F17" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="4">
         <v>1103</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D18" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E12">
+      <c r="E18" s="5">
         <v>201003</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F18" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1">
         <v>1104</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E13">
+      <c r="E19" s="2">
         <v>202001</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F19" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4">
         <v>1105</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C20" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E14">
+      <c r="E20" s="5">
         <v>202002</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F20" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1">
         <v>1106</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E15">
+      <c r="E21" s="2">
         <v>202003</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F21" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="4">
         <v>1201</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16">
+      <c r="D22" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="5">
         <v>101011</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F22" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1">
         <v>1202</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B23" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17">
+      <c r="D23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="2">
         <v>101012</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F23" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="4">
         <v>1203</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B24" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18">
+      <c r="D24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="5">
         <v>101013</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F24" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1">
         <v>1204</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B25" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19">
+      <c r="D25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="2">
         <v>101021</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F25" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="4">
         <v>1205</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20">
+      <c r="D26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="5">
         <v>101022</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F26" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="1">
         <v>1206</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21">
+      <c r="D27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="2">
         <v>101023</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F27" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="4">
         <v>1301</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B28" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C28" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22">
+      <c r="D28" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="5">
         <v>110001</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F28" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="1">
         <v>1302</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23">
+      <c r="D29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="2">
         <v>110002</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F29" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="4">
         <v>1303</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B30" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C30" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24">
+      <c r="D30" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="5">
         <v>110003</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F30" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="1">
         <v>1304</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C31" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25">
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2">
         <v>110004</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F31" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="4">
         <v>1305</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B32" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C32" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26">
+      <c r="D32" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="5">
         <v>110005</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F32" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="1">
         <v>1401</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C33" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D27" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27">
+      <c r="D33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="2">
         <v>111001</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F33" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="4">
         <v>1402</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B34" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C34" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28">
+      <c r="D34" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="5">
         <v>111002</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F34" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="1">
         <v>1403</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B35" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D29" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29">
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="2">
         <v>111003</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F35" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="4">
         <v>1404</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B36" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C36" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D30" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30">
+      <c r="D36" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="5">
         <v>111004</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F36" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="1">
         <v>1405</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B37" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C37" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31">
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="2">
         <v>111005</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F37" s="3" t="s">
         <v>73</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmung\Desktop\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B676EC1B-D469-46E1-9B79-299A31514629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="6189" windowHeight="14794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="6195" windowHeight="14790"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="110">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -337,12 +336,98 @@
   <si>
     <t>티타늄 자재</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_miner2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>copper_miner3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>copper_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_processor2</t>
+  </si>
+  <si>
+    <t>구리 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>copper_processor3</t>
+  </si>
+  <si>
+    <t>구리 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>iron_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_miner2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>iron_miner3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>iron_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_processor2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>iron_processor3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 가공 시설 Lv.3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -374,7 +459,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -419,13 +504,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -447,6 +563,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -465,15 +590,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:F37" totalsRowShown="0">
-  <autoFilter ref="A1:F37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F49" totalsRowShown="0">
+  <autoFilter ref="A1:F49"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ItemType"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="UnitId"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ItemIcon"/>
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="4" name="Name"/>
+    <tableColumn id="2" name="DisplayName"/>
+    <tableColumn id="5" name="ItemType"/>
+    <tableColumn id="6" name="UnitId"/>
+    <tableColumn id="3" name="ItemIcon"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -741,17 +866,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="5" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="4" max="5" width="17.875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -771,7 +896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -788,7 +913,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -805,7 +930,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -822,7 +947,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -839,7 +964,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -856,7 +981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -873,7 +998,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -890,7 +1015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -907,7 +1032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -924,7 +1049,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -941,7 +1066,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1011</v>
       </c>
@@ -958,7 +1083,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1012</v>
       </c>
@@ -975,7 +1100,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1013</v>
       </c>
@@ -992,7 +1117,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1014</v>
       </c>
@@ -1009,7 +1134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>1101</v>
       </c>
@@ -1029,7 +1154,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1102</v>
       </c>
@@ -1049,7 +1174,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>1103</v>
       </c>
@@ -1069,7 +1194,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1104</v>
       </c>
@@ -1089,7 +1214,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>1105</v>
       </c>
@@ -1109,7 +1234,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1106</v>
       </c>
@@ -1129,7 +1254,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>1201</v>
       </c>
@@ -1149,7 +1274,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>1202</v>
       </c>
@@ -1169,7 +1294,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>1203</v>
       </c>
@@ -1189,7 +1314,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>1204</v>
       </c>
@@ -1209,7 +1334,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>1205</v>
       </c>
@@ -1229,7 +1354,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>1206</v>
       </c>
@@ -1249,203 +1374,443 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="4">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>1207</v>
+      </c>
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28">
+        <v>102011</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>1208</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29">
+        <v>102012</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>1209</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30">
+        <v>102013</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>1210</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31">
+        <v>102021</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>1211</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32">
+        <v>102022</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>1212</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33">
+        <v>102023</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>1213</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34">
+        <v>103011</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>1214</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35">
+        <v>103012</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>1215</v>
+      </c>
+      <c r="B36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36">
+        <v>103013</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>1216</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37">
+        <v>103021</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>1217</v>
+      </c>
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38">
+        <v>103022</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>1218</v>
+      </c>
+      <c r="B39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39">
+        <v>103023</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
         <v>1301</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B40" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="D40" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="5">
         <v>110001</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F40" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="1">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
         <v>1302</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="2">
+      <c r="D41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="2">
         <v>110002</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F41" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="4">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
         <v>1303</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="5">
+      <c r="D42" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="5">
         <v>110003</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F42" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="1">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
         <v>1304</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="D43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="2">
         <v>110004</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F43" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="4">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
         <v>1305</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="5">
+      <c r="D44" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="5">
         <v>110005</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F44" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="1">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
         <v>1401</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="2">
+      <c r="D45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" s="2">
         <v>111001</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="4">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
         <v>1402</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="D46" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="5">
         <v>111002</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F46" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="1">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
         <v>1403</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="2">
+      <c r="D47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E47" s="2">
         <v>111003</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="4">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
         <v>1404</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="5">
+      <c r="D48" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="5">
         <v>111004</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F48" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="1">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="7">
         <v>1405</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B49" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C49" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="2">
+      <c r="D49" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="8">
         <v>111005</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F49" s="9" t="s">
         <v>73</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="172">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,50 +170,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UnitId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>stone_miner1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stone_miner2</t>
-  </si>
-  <si>
-    <t>stone_miner3</t>
-  </si>
-  <si>
     <t>stone_processor1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stone_processor2</t>
-  </si>
-  <si>
-    <t>stone_processor3</t>
-  </si>
-  <si>
     <t>돌 채굴 시설 Lv.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>돌 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>돌 채굴 시설 Lv.3</t>
-  </si>
-  <si>
     <t>돌 가공 시설 Lv.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>돌 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>돌 가공 시설 Lv.3</t>
-  </si>
-  <si>
     <t>Facility</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -314,14 +286,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>옵시디언 광물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>옵시디언 자재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>텅스텐 광물</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -422,6 +386,251 @@
   </si>
   <si>
     <t>철 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>흑요석 광물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 자재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lab6</t>
+  </si>
+  <si>
+    <t>연구소 Lv.6</t>
+  </si>
+  <si>
+    <t>lab7</t>
+  </si>
+  <si>
+    <t>연구소 Lv.7</t>
+  </si>
+  <si>
+    <t>engineMerger6</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>engineMerger7</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource_merger2</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>resource_merger3</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>resource_merger4</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>resource_merger5</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>resource_merger6</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>resource_merger7</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>resource_merger1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner2</t>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>gold_miner3</t>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_processor2</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>gold_processor3</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>obsidian_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner2</t>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner3</t>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_processor2</t>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>obsidian_processor3</t>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>tunstein_miner2</t>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>tunstein_miner3</t>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>tunstein_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_processor2</t>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>tunstein_processor3</t>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>titanium_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>titanium_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_processor2</t>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>titanium_processor3</t>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -590,14 +799,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F49" totalsRowShown="0">
-  <autoFilter ref="A1:F49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F80" totalsRowShown="0">
+  <autoFilter ref="A1:F80"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="4" name="Name"/>
     <tableColumn id="2" name="DisplayName"/>
     <tableColumn id="5" name="ItemType"/>
-    <tableColumn id="6" name="UnitId"/>
+    <tableColumn id="6" name="EntityId"/>
     <tableColumn id="3" name="ItemIcon"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -867,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.875" customWidth="1"/>
@@ -890,7 +1099,7 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -1037,10 +1246,10 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
@@ -1054,10 +1263,10 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
@@ -1071,10 +1280,10 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
@@ -1088,10 +1297,10 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
@@ -1105,10 +1314,10 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
@@ -1122,10 +1331,10 @@
         <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
@@ -1259,13 +1468,13 @@
         <v>1201</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E22" s="5">
         <v>101011</v>
@@ -1276,99 +1485,99 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2">
-        <v>101012</v>
+        <v>101021</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
-        <v>1203</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="5">
-        <v>101013</v>
-      </c>
-      <c r="F24" s="6" t="s">
+      <c r="A24" s="1">
+        <v>1207</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24">
+        <v>102011</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>1204</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>48</v>
+        <v>1208</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="2">
-        <v>101021</v>
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <v>102012</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
-        <v>1205</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="5">
-        <v>101022</v>
-      </c>
-      <c r="F26" s="6" t="s">
+      <c r="A26" s="1">
+        <v>1209</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26">
+        <v>102013</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>1206</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>50</v>
+        <v>1210</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27" s="2">
-        <v>101023</v>
+        <v>42</v>
+      </c>
+      <c r="E27">
+        <v>102021</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>37</v>
@@ -1376,19 +1585,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E28">
-        <v>102011</v>
+        <v>102022</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>37</v>
@@ -1396,19 +1605,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E29">
-        <v>102012</v>
+        <v>102023</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>37</v>
@@ -1416,19 +1625,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E30">
-        <v>102013</v>
+        <v>103011</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>37</v>
@@ -1436,19 +1645,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E31">
-        <v>102021</v>
+        <v>103012</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>37</v>
@@ -1456,19 +1665,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E32">
-        <v>102022</v>
+        <v>103013</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>37</v>
@@ -1476,19 +1685,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E33">
-        <v>102023</v>
+        <v>103021</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>37</v>
@@ -1496,19 +1705,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E34">
-        <v>103011</v>
+        <v>103022</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>37</v>
@@ -1516,19 +1725,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E35">
-        <v>103012</v>
+        <v>103023</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>37</v>
@@ -1536,19 +1745,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E36">
-        <v>103013</v>
+        <v>104011</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>37</v>
@@ -1556,19 +1765,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E37">
-        <v>103021</v>
+        <v>104012</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>37</v>
@@ -1576,19 +1785,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E38">
-        <v>103022</v>
+        <v>104013</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>37</v>
@@ -1596,222 +1805,821 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E39">
-        <v>103023</v>
+        <v>104021</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
-        <v>1301</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" s="5">
-        <v>110001</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>72</v>
+      <c r="A40" s="1">
+        <v>1223</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40">
+        <v>104022</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>1302</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>54</v>
+        <v>1224</v>
+      </c>
+      <c r="B41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>131</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="2">
-        <v>110002</v>
+        <v>42</v>
+      </c>
+      <c r="E41">
+        <v>104023</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
-        <v>1303</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="5">
-        <v>110003</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>72</v>
+      <c r="A42" s="1">
+        <v>1225</v>
+      </c>
+      <c r="B42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E42">
+        <v>105011</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>1304</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>56</v>
+        <v>1226</v>
+      </c>
+      <c r="B43" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" t="s">
+        <v>134</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="2">
-        <v>110004</v>
+        <v>42</v>
+      </c>
+      <c r="E43">
+        <v>105012</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
-        <v>1305</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="5">
-        <v>110005</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>72</v>
+      <c r="A44" s="1">
+        <v>1227</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>136</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44">
+        <v>105013</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>1401</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>63</v>
+        <v>1228</v>
+      </c>
+      <c r="B45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>138</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="2">
-        <v>111001</v>
+        <v>42</v>
+      </c>
+      <c r="E45">
+        <v>105021</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
-        <v>1402</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="5">
-        <v>111002</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>73</v>
+      <c r="A46" s="1">
+        <v>1229</v>
+      </c>
+      <c r="B46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46">
+        <v>105022</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
+        <v>1230</v>
+      </c>
+      <c r="B47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47">
+        <v>105023</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>1231</v>
+      </c>
+      <c r="B48" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E48">
+        <v>106011</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>1232</v>
+      </c>
+      <c r="B49" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E49">
+        <v>106012</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>1233</v>
+      </c>
+      <c r="B50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50">
+        <v>106013</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>1234</v>
+      </c>
+      <c r="B51" t="s">
+        <v>147</v>
+      </c>
+      <c r="C51" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51">
+        <v>106021</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>1235</v>
+      </c>
+      <c r="B52" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" t="s">
+        <v>149</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52">
+        <v>106022</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>1236</v>
+      </c>
+      <c r="B53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" t="s">
+        <v>151</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53">
+        <v>106023</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>1237</v>
+      </c>
+      <c r="B54" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54">
+        <v>107011</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>1238</v>
+      </c>
+      <c r="B55" t="s">
+        <v>153</v>
+      </c>
+      <c r="C55" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55">
+        <v>107012</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>1239</v>
+      </c>
+      <c r="B56" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" t="s">
+        <v>163</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E56">
+        <v>107013</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>1240</v>
+      </c>
+      <c r="B57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C57" t="s">
+        <v>164</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E57">
+        <v>107021</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>1241</v>
+      </c>
+      <c r="B58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C58" t="s">
+        <v>157</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E58">
+        <v>107022</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>1242</v>
+      </c>
+      <c r="B59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C59" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59">
+        <v>107023</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
+        <v>1301</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E60" s="5">
+        <v>110001</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>1302</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E61" s="2">
+        <v>110002</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
+        <v>1303</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E62" s="5">
+        <v>110003</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>1304</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" s="2">
+        <v>110004</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
+        <v>1305</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E64" s="5">
+        <v>110005</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1306</v>
+      </c>
+      <c r="B65" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" t="s">
+        <v>42</v>
+      </c>
+      <c r="E65">
+        <v>110006</v>
+      </c>
+      <c r="F65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1307</v>
+      </c>
+      <c r="B66" t="s">
+        <v>103</v>
+      </c>
+      <c r="C66" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" t="s">
+        <v>42</v>
+      </c>
+      <c r="E66">
+        <v>110007</v>
+      </c>
+      <c r="F66" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>1401</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E67" s="2">
+        <v>111001</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="4">
+        <v>1402</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E68" s="5">
+        <v>111002</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
         <v>1403</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E47" s="2">
+      <c r="B69" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E69" s="2">
         <v>111003</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+      <c r="F69" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
         <v>1404</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" s="5">
+      <c r="B70" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E70" s="5">
         <v>111004</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="7">
+      <c r="F70" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="7">
         <v>1405</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="8">
+      <c r="B71" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" s="8">
         <v>111005</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>73</v>
+      <c r="F71" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="7">
+        <v>1406</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E72" s="8">
+        <v>111006</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="7">
+        <v>1407</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E73" s="8">
+        <v>111007</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>1501</v>
+      </c>
+      <c r="B74" t="s">
+        <v>122</v>
+      </c>
+      <c r="C74" t="s">
+        <v>109</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E74">
+        <v>113001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>1502</v>
+      </c>
+      <c r="B75" t="s">
+        <v>110</v>
+      </c>
+      <c r="C75" t="s">
+        <v>111</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E75">
+        <v>113002</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>1503</v>
+      </c>
+      <c r="B76" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" t="s">
+        <v>113</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E76">
+        <v>113003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>1504</v>
+      </c>
+      <c r="B77" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" t="s">
+        <v>115</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E77">
+        <v>113004</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>1505</v>
+      </c>
+      <c r="B78" t="s">
+        <v>116</v>
+      </c>
+      <c r="C78" t="s">
+        <v>117</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E78">
+        <v>113005</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>1506</v>
+      </c>
+      <c r="B79" t="s">
+        <v>118</v>
+      </c>
+      <c r="C79" t="s">
+        <v>119</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E79">
+        <v>113006</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>1507</v>
+      </c>
+      <c r="B80" t="s">
+        <v>120</v>
+      </c>
+      <c r="C80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E80">
+        <v>113007</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="173">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -630,6 +630,10 @@
   </si>
   <si>
     <t>EntityId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resourceMergerIcon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1484,8 +1488,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>1204</v>
+      <c r="A23" s="4">
+        <v>1202</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>39</v>
@@ -1504,8 +1508,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>1207</v>
+      <c r="A24" s="4">
+        <v>1203</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
@@ -1524,8 +1528,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>1208</v>
+      <c r="A25" s="4">
+        <v>1204</v>
       </c>
       <c r="B25" t="s">
         <v>77</v>
@@ -1544,8 +1548,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>1209</v>
+      <c r="A26" s="4">
+        <v>1205</v>
       </c>
       <c r="B26" t="s">
         <v>79</v>
@@ -1564,8 +1568,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>1210</v>
+      <c r="A27" s="4">
+        <v>1206</v>
       </c>
       <c r="B27" t="s">
         <v>81</v>
@@ -1584,8 +1588,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>1211</v>
+      <c r="A28" s="4">
+        <v>1207</v>
       </c>
       <c r="B28" t="s">
         <v>83</v>
@@ -1604,8 +1608,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>1212</v>
+      <c r="A29" s="4">
+        <v>1208</v>
       </c>
       <c r="B29" t="s">
         <v>85</v>
@@ -1624,8 +1628,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>1213</v>
+      <c r="A30" s="4">
+        <v>1209</v>
       </c>
       <c r="B30" t="s">
         <v>87</v>
@@ -1644,8 +1648,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>1214</v>
+      <c r="A31" s="4">
+        <v>1210</v>
       </c>
       <c r="B31" t="s">
         <v>89</v>
@@ -1664,8 +1668,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>1215</v>
+      <c r="A32" s="4">
+        <v>1211</v>
       </c>
       <c r="B32" t="s">
         <v>91</v>
@@ -1684,8 +1688,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
-        <v>1216</v>
+      <c r="A33" s="4">
+        <v>1212</v>
       </c>
       <c r="B33" t="s">
         <v>93</v>
@@ -1704,8 +1708,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>1217</v>
+      <c r="A34" s="4">
+        <v>1213</v>
       </c>
       <c r="B34" t="s">
         <v>95</v>
@@ -1724,8 +1728,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>1218</v>
+      <c r="A35" s="4">
+        <v>1214</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
@@ -1744,8 +1748,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
-        <v>1219</v>
+      <c r="A36" s="4">
+        <v>1215</v>
       </c>
       <c r="B36" t="s">
         <v>165</v>
@@ -1764,8 +1768,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
-        <v>1220</v>
+      <c r="A37" s="4">
+        <v>1216</v>
       </c>
       <c r="B37" t="s">
         <v>123</v>
@@ -1784,8 +1788,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
-        <v>1221</v>
+      <c r="A38" s="4">
+        <v>1217</v>
       </c>
       <c r="B38" t="s">
         <v>125</v>
@@ -1804,8 +1808,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <v>1222</v>
+      <c r="A39" s="4">
+        <v>1218</v>
       </c>
       <c r="B39" t="s">
         <v>167</v>
@@ -1824,8 +1828,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
-        <v>1223</v>
+      <c r="A40" s="4">
+        <v>1219</v>
       </c>
       <c r="B40" t="s">
         <v>128</v>
@@ -1844,8 +1848,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <v>1224</v>
+      <c r="A41" s="4">
+        <v>1220</v>
       </c>
       <c r="B41" t="s">
         <v>130</v>
@@ -1864,8 +1868,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <v>1225</v>
+      <c r="A42" s="4">
+        <v>1221</v>
       </c>
       <c r="B42" t="s">
         <v>132</v>
@@ -1884,8 +1888,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <v>1226</v>
+      <c r="A43" s="4">
+        <v>1222</v>
       </c>
       <c r="B43" t="s">
         <v>133</v>
@@ -1904,8 +1908,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <v>1227</v>
+      <c r="A44" s="4">
+        <v>1223</v>
       </c>
       <c r="B44" t="s">
         <v>135</v>
@@ -1924,8 +1928,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <v>1228</v>
+      <c r="A45" s="4">
+        <v>1224</v>
       </c>
       <c r="B45" t="s">
         <v>137</v>
@@ -1944,8 +1948,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
-        <v>1229</v>
+      <c r="A46" s="4">
+        <v>1225</v>
       </c>
       <c r="B46" t="s">
         <v>139</v>
@@ -1964,8 +1968,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
-        <v>1230</v>
+      <c r="A47" s="4">
+        <v>1226</v>
       </c>
       <c r="B47" t="s">
         <v>141</v>
@@ -1984,8 +1988,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
-        <v>1231</v>
+      <c r="A48" s="4">
+        <v>1227</v>
       </c>
       <c r="B48" t="s">
         <v>168</v>
@@ -2004,8 +2008,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
-        <v>1232</v>
+      <c r="A49" s="4">
+        <v>1228</v>
       </c>
       <c r="B49" t="s">
         <v>143</v>
@@ -2024,8 +2028,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
-        <v>1233</v>
+      <c r="A50" s="4">
+        <v>1229</v>
       </c>
       <c r="B50" t="s">
         <v>145</v>
@@ -2044,8 +2048,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
-        <v>1234</v>
+      <c r="A51" s="4">
+        <v>1230</v>
       </c>
       <c r="B51" t="s">
         <v>147</v>
@@ -2064,8 +2068,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
-        <v>1235</v>
+      <c r="A52" s="4">
+        <v>1231</v>
       </c>
       <c r="B52" t="s">
         <v>148</v>
@@ -2084,8 +2088,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
-        <v>1236</v>
+      <c r="A53" s="4">
+        <v>1232</v>
       </c>
       <c r="B53" t="s">
         <v>150</v>
@@ -2104,8 +2108,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
-        <v>1237</v>
+      <c r="A54" s="4">
+        <v>1233</v>
       </c>
       <c r="B54" t="s">
         <v>152</v>
@@ -2124,8 +2128,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
-        <v>1238</v>
+      <c r="A55" s="4">
+        <v>1234</v>
       </c>
       <c r="B55" t="s">
         <v>153</v>
@@ -2144,8 +2148,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
-        <v>1239</v>
+      <c r="A56" s="4">
+        <v>1235</v>
       </c>
       <c r="B56" t="s">
         <v>170</v>
@@ -2164,8 +2168,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
-        <v>1240</v>
+      <c r="A57" s="4">
+        <v>1236</v>
       </c>
       <c r="B57" t="s">
         <v>155</v>
@@ -2184,8 +2188,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
-        <v>1241</v>
+      <c r="A58" s="4">
+        <v>1237</v>
       </c>
       <c r="B58" t="s">
         <v>156</v>
@@ -2204,8 +2208,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
-        <v>1242</v>
+      <c r="A59" s="4">
+        <v>1238</v>
       </c>
       <c r="B59" t="s">
         <v>158</v>
@@ -2519,6 +2523,9 @@
       <c r="E74">
         <v>113001</v>
       </c>
+      <c r="F74" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
@@ -2536,6 +2543,9 @@
       <c r="E75">
         <v>113002</v>
       </c>
+      <c r="F75" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
@@ -2553,6 +2563,9 @@
       <c r="E76">
         <v>113003</v>
       </c>
+      <c r="F76" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
@@ -2570,6 +2583,9 @@
       <c r="E77">
         <v>113004</v>
       </c>
+      <c r="F77" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
@@ -2587,6 +2603,9 @@
       <c r="E78">
         <v>113005</v>
       </c>
+      <c r="F78" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
@@ -2604,6 +2623,9 @@
       <c r="E79">
         <v>113006</v>
       </c>
+      <c r="F79" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
@@ -2620,6 +2642,9 @@
       </c>
       <c r="E80">
         <v>113007</v>
+      </c>
+      <c r="F80" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="201">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,507 +134,600 @@
     <t>RedEngine_3</t>
   </si>
   <si>
+    <t>빨강 엔진 Lv.2</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.3</t>
+  </si>
+  <si>
+    <t>Engine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ironIngot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Facility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lab1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구소 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연구소 Lv.2</t>
+  </si>
+  <si>
+    <t>연구소 Lv.3</t>
+  </si>
+  <si>
+    <t>연구소 Lv.4</t>
+  </si>
+  <si>
+    <t>연구소 Lv.5</t>
+  </si>
+  <si>
+    <t>lab2</t>
+  </si>
+  <si>
+    <t>lab3</t>
+  </si>
+  <si>
+    <t>lab4</t>
+  </si>
+  <si>
+    <t>lab5</t>
+  </si>
+  <si>
+    <t>engineMerger1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMerger2</t>
+  </si>
+  <si>
+    <t>engineMerger3</t>
+  </si>
+  <si>
+    <t>engineMerger4</t>
+  </si>
+  <si>
+    <t>engineMerger5</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>labIcon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engineMergerIcon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obsidian_Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obsidian_Resource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tunstein_Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tunstein_Resource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Titanium_Material</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Titanium_Resource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 광물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 자재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 광물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 자재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_miner2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>copper_miner3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>copper_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구리 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_processor2</t>
+  </si>
+  <si>
+    <t>구리 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>copper_processor3</t>
+  </si>
+  <si>
+    <t>구리 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>iron_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_miner2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>iron_miner3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>iron_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_processor2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>iron_processor3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>흑요석 광물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 자재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lab6</t>
+  </si>
+  <si>
+    <t>연구소 Lv.6</t>
+  </si>
+  <si>
+    <t>lab7</t>
+  </si>
+  <si>
+    <t>연구소 Lv.7</t>
+  </si>
+  <si>
+    <t>engineMerger6</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>engineMerger7</t>
+  </si>
+  <si>
+    <t>엔진 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource_merger2</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.2</t>
+  </si>
+  <si>
+    <t>resource_merger3</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.3</t>
+  </si>
+  <si>
+    <t>resource_merger4</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.4</t>
+  </si>
+  <si>
+    <t>resource_merger5</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.5</t>
+  </si>
+  <si>
+    <t>resource_merger6</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.6</t>
+  </si>
+  <si>
+    <t>resource_merger7</t>
+  </si>
+  <si>
+    <t>자원 합성기 Lv.7</t>
+  </si>
+  <si>
+    <t>resource_merger1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner2</t>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>gold_miner3</t>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_processor2</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>gold_processor3</t>
+  </si>
+  <si>
+    <t>금 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>obsidian_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner2</t>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner3</t>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_processor2</t>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>obsidian_processor3</t>
+  </si>
+  <si>
+    <t>흑요석 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>tunstein_miner2</t>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>tunstein_miner3</t>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>tunstein_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_processor2</t>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>tunstein_processor3</t>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>titanium_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>titanium_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_processor2</t>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.2</t>
+  </si>
+  <si>
+    <t>titanium_processor3</t>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.3</t>
+  </si>
+  <si>
+    <t>흑요석 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 채굴 시설 Lv.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>티타늄 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 채굴 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_processor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_miner1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅스텐 가공 시설 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resourceMergerIcon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreenEngine_4</t>
+  </si>
+  <si>
     <t>초록 엔진 Lv.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>초록 엔진 Lv.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>초록 엔진 Lv.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>빨강 엔진 Lv.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>빨강 엔진 Lv.2</t>
-  </si>
-  <si>
-    <t>빨강 엔진 Lv.3</t>
-  </si>
-  <si>
-    <t>Engine</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ironIngot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stone_miner1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stone_processor1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 가공 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Facility</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lab1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연구소 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연구소 Lv.2</t>
-  </si>
-  <si>
-    <t>연구소 Lv.3</t>
-  </si>
-  <si>
-    <t>연구소 Lv.4</t>
-  </si>
-  <si>
-    <t>연구소 Lv.5</t>
-  </si>
-  <si>
-    <t>lab2</t>
-  </si>
-  <si>
-    <t>lab3</t>
-  </si>
-  <si>
-    <t>lab4</t>
-  </si>
-  <si>
-    <t>lab5</t>
-  </si>
-  <si>
-    <t>engineMerger1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMerger2</t>
-  </si>
-  <si>
-    <t>engineMerger3</t>
-  </si>
-  <si>
-    <t>engineMerger4</t>
-  </si>
-  <si>
-    <t>engineMerger5</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.2</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.3</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.4</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.5</t>
-  </si>
-  <si>
-    <t>labIcon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMergerIcon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Obsidian_Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Obsidian_Resource</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tunstein_Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tunstein_Resource</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Titanium_Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Titanium_Resource</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅스텐 광물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅스텐 자재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 광물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 자재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>copper_miner1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>copper_miner2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>copper_miner3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 채굴 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>copper_processor1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구리 가공 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>copper_processor2</t>
-  </si>
-  <si>
-    <t>구리 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>copper_processor3</t>
-  </si>
-  <si>
-    <t>구리 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>iron_miner1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iron_miner2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>iron_miner3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 채굴 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>iron_processor1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 가공 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iron_processor2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>iron_processor3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>흑요석 광물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 자재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lab6</t>
-  </si>
-  <si>
-    <t>연구소 Lv.6</t>
-  </si>
-  <si>
-    <t>lab7</t>
-  </si>
-  <si>
-    <t>연구소 Lv.7</t>
-  </si>
-  <si>
-    <t>engineMerger6</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.6</t>
-  </si>
-  <si>
-    <t>engineMerger7</t>
-  </si>
-  <si>
-    <t>엔진 합성기 Lv.7</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>resource_merger2</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.2</t>
-  </si>
-  <si>
-    <t>resource_merger3</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.3</t>
-  </si>
-  <si>
-    <t>resource_merger4</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.4</t>
-  </si>
-  <si>
-    <t>resource_merger5</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.5</t>
-  </si>
-  <si>
-    <t>resource_merger6</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.6</t>
-  </si>
-  <si>
-    <t>resource_merger7</t>
-  </si>
-  <si>
-    <t>자원 합성기 Lv.7</t>
-  </si>
-  <si>
-    <t>resource_merger1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gold_miner2</t>
-  </si>
-  <si>
-    <t>금 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>gold_miner3</t>
-  </si>
-  <si>
-    <t>금 채굴 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>금 가공 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gold_processor2</t>
-  </si>
-  <si>
-    <t>금 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>gold_processor3</t>
-  </si>
-  <si>
-    <t>금 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>obsidian_miner1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>obsidian_miner2</t>
-  </si>
-  <si>
-    <t>흑요석 채굴 시설 Lv.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>obsidian_miner3</t>
-  </si>
-  <si>
-    <t>흑요석 채굴 시설 Lv.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>obsidian_processor1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑요석 가공 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>obsidian_processor2</t>
-  </si>
-  <si>
-    <t>흑요석 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>obsidian_processor3</t>
-  </si>
-  <si>
-    <t>흑요석 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>tunstein_miner2</t>
-  </si>
-  <si>
-    <t>텅스텐 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>tunstein_miner3</t>
-  </si>
-  <si>
-    <t>텅스텐 채굴 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>tunstein_processor1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tunstein_processor2</t>
-  </si>
-  <si>
-    <t>텅스텐 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>tunstein_processor3</t>
-  </si>
-  <si>
-    <t>텅스텐 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>titanium_miner1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>titanium_miner2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 채굴 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>titanium_processor1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>titanium_processor2</t>
-  </si>
-  <si>
-    <t>티타늄 가공 시설 Lv.2</t>
-  </si>
-  <si>
-    <t>titanium_processor3</t>
-  </si>
-  <si>
-    <t>티타늄 가공 시설 Lv.3</t>
-  </si>
-  <si>
-    <t>흑요석 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅스텐 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 채굴 시설 Lv.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>티타늄 가공 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gold_miner1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금 채굴 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gold_processor1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tunstein_miner1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅스텐 가공 시설 Lv.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>titanium_miner3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EntityId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>resourceMergerIcon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>빨강 엔진 Lv.4</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.2</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.3</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.4</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.2</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.3</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.4</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.2</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.3</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.4</t>
+  </si>
+  <si>
+    <t>RedEngine_4</t>
+  </si>
+  <si>
+    <t>BlueEngine_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BlueEngine_2</t>
+  </si>
+  <si>
+    <t>BlueEngine_3</t>
+  </si>
+  <si>
+    <t>BlueEngine_4</t>
+  </si>
+  <si>
+    <t>PurpleEngine_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PurpleEngine_2</t>
+  </si>
+  <si>
+    <t>PurpleEngine_3</t>
+  </si>
+  <si>
+    <t>PurpleEngine_4</t>
+  </si>
+  <si>
+    <t>YellowEngine_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YellowEngine_2</t>
+  </si>
+  <si>
+    <t>YellowEngine_3</t>
+  </si>
+  <si>
+    <t>YellowEngine_4</t>
   </si>
 </sst>
 </file>
@@ -803,8 +896,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F80" totalsRowShown="0">
-  <autoFilter ref="A1:F80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F94" totalsRowShown="0">
+  <autoFilter ref="A1:F94"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="4" name="Name"/>
@@ -1080,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.875" customWidth="1"/>
@@ -1103,7 +1196,7 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -1123,7 +1216,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1140,7 +1233,7 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1157,7 +1250,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1174,7 +1267,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1191,7 +1284,7 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1208,7 +1301,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1225,7 +1318,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1242,7 +1335,7 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1250,16 +1343,16 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1267,16 +1360,16 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1284,16 +1377,16 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
         <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1301,16 +1394,16 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
         <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1318,16 +1411,16 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
         <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>73</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1335,1316 +1428,1596 @@
         <v>1014</v>
       </c>
       <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
         <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>1101</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>28</v>
+      <c r="C16" t="s">
+        <v>170</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="5">
+        <v>30</v>
+      </c>
+      <c r="E16">
         <v>201001</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1102</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="C17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17">
         <v>201002</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>37</v>
+      <c r="F17" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>1103</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="E18">
         <v>201003</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19" s="4">
         <v>1104</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="2">
-        <v>202001</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>37</v>
+      <c r="B19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19">
+        <v>201004</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
-        <v>1105</v>
-      </c>
-      <c r="B20" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20">
+        <v>202001</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>1112</v>
+      </c>
+      <c r="B21" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21">
         <v>202002</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>1106</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="2">
-        <v>202003</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>37</v>
+      <c r="F21" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
-        <v>1201</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>40</v>
+        <v>1113</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="5">
-        <v>101011</v>
+        <v>30</v>
+      </c>
+      <c r="E22">
+        <v>202003</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
-        <v>1202</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="2">
-        <v>101021</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>37</v>
+        <v>1114</v>
+      </c>
+      <c r="B23" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>202004</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
-        <v>1203</v>
+        <v>1121</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>176</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E24">
-        <v>102011</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>37</v>
+        <v>203001</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
-        <v>1204</v>
+        <v>1122</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>177</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E25">
-        <v>102012</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>37</v>
+        <v>203002</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
-        <v>1205</v>
+        <v>1123</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>178</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E26">
-        <v>102013</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>37</v>
+        <v>203003</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>1206</v>
+        <v>1124</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>42</v>
+        <v>179</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E27">
-        <v>102021</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>37</v>
+        <v>203004</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
-        <v>1207</v>
+        <v>1131</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>180</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E28">
-        <v>102022</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>37</v>
+        <v>204001</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>1208</v>
+        <v>1132</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>42</v>
+        <v>181</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E29">
-        <v>102023</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>37</v>
+        <v>204002</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>1209</v>
+        <v>1133</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>195</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>42</v>
+        <v>182</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E30">
-        <v>103011</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>37</v>
+        <v>204003</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
-        <v>1210</v>
+        <v>1134</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>196</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>42</v>
+        <v>183</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E31">
-        <v>103012</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>37</v>
+        <v>204004</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
-        <v>1211</v>
+        <v>1141</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>197</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>42</v>
+        <v>184</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E32">
-        <v>103013</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>37</v>
+        <v>205001</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
-        <v>1212</v>
+        <v>1142</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>42</v>
+        <v>185</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E33">
-        <v>103021</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>37</v>
+        <v>205002</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
-        <v>1213</v>
+        <v>1143</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>42</v>
+        <v>186</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E34">
-        <v>103022</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>37</v>
+        <v>205003</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>1214</v>
+        <v>1144</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>42</v>
+        <v>187</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E35">
-        <v>103023</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>37</v>
+        <v>205004</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>1215</v>
-      </c>
-      <c r="B36" t="s">
-        <v>165</v>
-      </c>
-      <c r="C36" t="s">
-        <v>166</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E36">
-        <v>104011</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>37</v>
+        <v>1201</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="5">
+        <v>101011</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <v>1216</v>
-      </c>
-      <c r="B37" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" t="s">
-        <v>124</v>
+        <v>1202</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E37">
-        <v>104012</v>
+        <v>38</v>
+      </c>
+      <c r="E37" s="2">
+        <v>101021</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <v>1217</v>
+        <v>1203</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E38">
-        <v>104013</v>
+        <v>102011</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <v>1218</v>
+        <v>1204</v>
       </c>
       <c r="B39" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E39">
-        <v>104021</v>
+        <v>102012</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
-        <v>1219</v>
+        <v>1205</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E40">
-        <v>104022</v>
+        <v>102013</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
-        <v>1220</v>
+        <v>1206</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E41">
-        <v>104023</v>
+        <v>102021</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
-        <v>1221</v>
+        <v>1207</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E42">
-        <v>105011</v>
+        <v>102022</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
-        <v>1222</v>
+        <v>1208</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E43">
-        <v>105012</v>
+        <v>102023</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
-        <v>1223</v>
+        <v>1209</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E44">
-        <v>105013</v>
+        <v>103011</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
-        <v>1224</v>
+        <v>1210</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E45">
-        <v>105021</v>
+        <v>103012</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
-        <v>1225</v>
+        <v>1211</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E46">
-        <v>105022</v>
+        <v>103013</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
-        <v>1226</v>
+        <v>1212</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E47">
-        <v>105023</v>
+        <v>103021</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
-        <v>1227</v>
+        <v>1213</v>
       </c>
       <c r="B48" t="s">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="C48" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E48">
-        <v>106011</v>
+        <v>103022</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
-        <v>1228</v>
+        <v>1214</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E49">
-        <v>106012</v>
+        <v>103023</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
-        <v>1229</v>
+        <v>1215</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E50">
-        <v>106013</v>
+        <v>104011</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
-        <v>1230</v>
+        <v>1216</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="C51" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E51">
-        <v>106021</v>
+        <v>104012</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
-        <v>1231</v>
+        <v>1217</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="C52" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E52">
-        <v>106022</v>
+        <v>104013</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
-        <v>1232</v>
+        <v>1218</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C53" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E53">
-        <v>106023</v>
+        <v>104021</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
-        <v>1233</v>
+        <v>1219</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="C54" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E54">
-        <v>107011</v>
+        <v>104022</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
-        <v>1234</v>
+        <v>1220</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E55">
-        <v>107012</v>
+        <v>104023</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
-        <v>1235</v>
+        <v>1221</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E56">
-        <v>107013</v>
+        <v>105011</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
-        <v>1236</v>
+        <v>1222</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E57">
-        <v>107021</v>
+        <v>105012</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
-        <v>1237</v>
+        <v>1223</v>
       </c>
       <c r="B58" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E58">
-        <v>107022</v>
+        <v>105013</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
-        <v>1238</v>
+        <v>1224</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E59">
-        <v>107023</v>
+        <v>105021</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
-        <v>1301</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E60" s="5">
-        <v>110001</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>63</v>
+        <v>1225</v>
+      </c>
+      <c r="B60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" t="s">
+        <v>136</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60">
+        <v>105022</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
-        <v>1302</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>45</v>
+      <c r="A61" s="4">
+        <v>1226</v>
+      </c>
+      <c r="B61" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" t="s">
+        <v>138</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E61" s="2">
-        <v>110002</v>
+        <v>38</v>
+      </c>
+      <c r="E61">
+        <v>105023</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
-        <v>1303</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E62" s="5">
-        <v>110003</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>63</v>
+        <v>1227</v>
+      </c>
+      <c r="B62" t="s">
+        <v>164</v>
+      </c>
+      <c r="C62" t="s">
+        <v>157</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E62">
+        <v>106011</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
-        <v>1304</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>47</v>
+      <c r="A63" s="4">
+        <v>1228</v>
+      </c>
+      <c r="B63" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" t="s">
+        <v>140</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E63" s="2">
-        <v>110004</v>
+        <v>38</v>
+      </c>
+      <c r="E63">
+        <v>106012</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
-        <v>1305</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E64" s="5">
-        <v>110005</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>63</v>
+        <v>1229</v>
+      </c>
+      <c r="B64" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64">
+        <v>106013</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>1306</v>
+      <c r="A65" s="4">
+        <v>1230</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="C65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D65" t="s">
-        <v>42</v>
+        <v>165</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E65">
-        <v>110006</v>
-      </c>
-      <c r="F65" t="s">
-        <v>63</v>
+        <v>106021</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>1307</v>
+      <c r="A66" s="4">
+        <v>1231</v>
       </c>
       <c r="B66" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
-      </c>
-      <c r="D66" t="s">
-        <v>42</v>
+        <v>145</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E66">
-        <v>110007</v>
-      </c>
-      <c r="F66" t="s">
-        <v>63</v>
+        <v>106022</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
-        <v>1401</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>54</v>
+      <c r="A67" s="4">
+        <v>1232</v>
+      </c>
+      <c r="B67" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67" t="s">
+        <v>147</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E67" s="2">
-        <v>111001</v>
+        <v>38</v>
+      </c>
+      <c r="E67">
+        <v>106023</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
-        <v>1402</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E68" s="5">
-        <v>111002</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>64</v>
+        <v>1233</v>
+      </c>
+      <c r="B68" t="s">
+        <v>148</v>
+      </c>
+      <c r="C68" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68">
+        <v>107011</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
-        <v>1403</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>60</v>
+      <c r="A69" s="4">
+        <v>1234</v>
+      </c>
+      <c r="B69" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" t="s">
+        <v>150</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E69" s="2">
-        <v>111003</v>
+        <v>38</v>
+      </c>
+      <c r="E69">
+        <v>107012</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
-        <v>1404</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D70" s="5" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" t="s">
+        <v>159</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E70">
+        <v>107013</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
+        <v>1236</v>
+      </c>
+      <c r="B71" t="s">
+        <v>151</v>
+      </c>
+      <c r="C71" t="s">
+        <v>160</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E71">
+        <v>107021</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="4">
+        <v>1237</v>
+      </c>
+      <c r="B72" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" t="s">
+        <v>153</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72">
+        <v>107022</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
+        <v>1238</v>
+      </c>
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E73">
+        <v>107023</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="4">
+        <v>1301</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E74" s="5">
+        <v>110001</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>1302</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" s="2">
+        <v>110002</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="4">
+        <v>1303</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E70" s="5">
-        <v>111004</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="7">
-        <v>1405</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E71" s="8">
-        <v>111005</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="7">
-        <v>1406</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E72" s="8">
-        <v>111006</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="7">
-        <v>1407</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E73" s="8">
-        <v>111007</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>1501</v>
-      </c>
-      <c r="B74" t="s">
-        <v>122</v>
-      </c>
-      <c r="C74" t="s">
-        <v>109</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E74">
-        <v>113001</v>
-      </c>
-      <c r="F74" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>1502</v>
-      </c>
-      <c r="B75" t="s">
-        <v>110</v>
-      </c>
-      <c r="C75" t="s">
-        <v>111</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E75">
-        <v>113002</v>
-      </c>
-      <c r="F75" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>1503</v>
-      </c>
-      <c r="B76" t="s">
-        <v>112</v>
-      </c>
-      <c r="C76" t="s">
-        <v>113</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E76">
-        <v>113003</v>
-      </c>
-      <c r="F76" t="s">
-        <v>172</v>
+      <c r="D76" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E76" s="5">
+        <v>110003</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>1504</v>
-      </c>
-      <c r="B77" t="s">
-        <v>114</v>
-      </c>
-      <c r="C77" t="s">
-        <v>115</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E77">
-        <v>113004</v>
-      </c>
-      <c r="F77" t="s">
-        <v>172</v>
+      <c r="A77" s="1">
+        <v>1304</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E77" s="2">
+        <v>110004</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>1505</v>
-      </c>
-      <c r="B78" t="s">
-        <v>116</v>
-      </c>
-      <c r="C78" t="s">
-        <v>117</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E78">
-        <v>113005</v>
-      </c>
-      <c r="F78" t="s">
-        <v>172</v>
+      <c r="A78" s="4">
+        <v>1305</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" s="5">
+        <v>110005</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1506</v>
+        <v>1306</v>
       </c>
       <c r="B79" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>119</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>42</v>
+        <v>98</v>
+      </c>
+      <c r="D79" t="s">
+        <v>38</v>
       </c>
       <c r="E79">
-        <v>113006</v>
+        <v>110006</v>
       </c>
       <c r="F79" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
+        <v>1307</v>
+      </c>
+      <c r="B80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D80" t="s">
+        <v>38</v>
+      </c>
+      <c r="E80">
+        <v>110007</v>
+      </c>
+      <c r="F80" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>1401</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" s="2">
+        <v>111001</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="4">
+        <v>1402</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E82" s="5">
+        <v>111002</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>1403</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" s="2">
+        <v>111003</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="4">
+        <v>1404</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E84" s="5">
+        <v>111004</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="7">
+        <v>1405</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E85" s="8">
+        <v>111005</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="7">
+        <v>1406</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E86" s="8">
+        <v>111006</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="7">
+        <v>1407</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" s="8">
+        <v>111007</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>1501</v>
+      </c>
+      <c r="B88" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88" t="s">
+        <v>105</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E88">
+        <v>113001</v>
+      </c>
+      <c r="F88" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>1502</v>
+      </c>
+      <c r="B89" t="s">
+        <v>106</v>
+      </c>
+      <c r="C89" t="s">
+        <v>107</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89">
+        <v>113002</v>
+      </c>
+      <c r="F89" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>1503</v>
+      </c>
+      <c r="B90" t="s">
+        <v>108</v>
+      </c>
+      <c r="C90" t="s">
+        <v>109</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E90">
+        <v>113003</v>
+      </c>
+      <c r="F90" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>1504</v>
+      </c>
+      <c r="B91" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91" t="s">
+        <v>111</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E91">
+        <v>113004</v>
+      </c>
+      <c r="F91" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>1505</v>
+      </c>
+      <c r="B92" t="s">
+        <v>112</v>
+      </c>
+      <c r="C92" t="s">
+        <v>113</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E92">
+        <v>113005</v>
+      </c>
+      <c r="F92" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>1506</v>
+      </c>
+      <c r="B93" t="s">
+        <v>114</v>
+      </c>
+      <c r="C93" t="s">
+        <v>115</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E93">
+        <v>113006</v>
+      </c>
+      <c r="F93" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94">
         <v>1507</v>
       </c>
-      <c r="B80" t="s">
-        <v>120</v>
-      </c>
-      <c r="C80" t="s">
-        <v>121</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E80">
+      <c r="B94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C94" t="s">
+        <v>117</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E94">
         <v>113007</v>
       </c>
-      <c r="F80" t="s">
-        <v>172</v>
+      <c r="F94" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="213">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,14 +144,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ironIngot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>engine_test</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -728,6 +720,62 @@
   </si>
   <si>
     <t>YellowEngine_4</t>
+  </si>
+  <si>
+    <t>Ingots_C1_128_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128_7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128_6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128.png_9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128.png_35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C3_128.png_44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C3_128.png_46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C2_128_56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128.png_23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128.png_32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C3_128.png_50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C1_128_9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C1_128_31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128_56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1179,7 +1227,7 @@
     <col min="2" max="2" width="17.875" customWidth="1"/>
     <col min="3" max="3" width="18.125" customWidth="1"/>
     <col min="4" max="5" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="6" max="6" width="35.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1196,7 +1244,7 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -1216,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1233,7 +1281,7 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1250,7 +1298,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1267,7 +1315,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1284,7 +1332,7 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1301,7 +1349,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1318,7 +1366,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1335,7 +1383,7 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1343,16 +1391,16 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1360,16 +1408,16 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1377,16 +1425,16 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1394,16 +1442,16 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1411,16 +1459,16 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1428,16 +1476,16 @@
         <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1448,7 +1496,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>30</v>
@@ -1457,7 +1505,7 @@
         <v>201001</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1468,7 +1516,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>30</v>
@@ -1477,7 +1525,7 @@
         <v>201002</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1488,7 +1536,7 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>30</v>
@@ -1497,7 +1545,7 @@
         <v>201003</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1505,10 +1553,10 @@
         <v>1104</v>
       </c>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>30</v>
@@ -1517,7 +1565,7 @@
         <v>201004</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1528,7 +1576,7 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>30</v>
@@ -1537,7 +1585,7 @@
         <v>202001</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1557,7 +1605,7 @@
         <v>202002</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1577,7 +1625,7 @@
         <v>202003</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1585,10 +1633,10 @@
         <v>1114</v>
       </c>
       <c r="B23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C23" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>30</v>
@@ -1597,7 +1645,7 @@
         <v>202004</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1605,10 +1653,10 @@
         <v>1121</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>30</v>
@@ -1617,7 +1665,7 @@
         <v>203001</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1625,10 +1673,10 @@
         <v>1122</v>
       </c>
       <c r="B25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>30</v>
@@ -1637,7 +1685,7 @@
         <v>203002</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1645,10 +1693,10 @@
         <v>1123</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>30</v>
@@ -1657,7 +1705,7 @@
         <v>203003</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1665,10 +1713,10 @@
         <v>1124</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C27" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>30</v>
@@ -1677,7 +1725,7 @@
         <v>203004</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1685,10 +1733,10 @@
         <v>1131</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C28" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>30</v>
@@ -1697,7 +1745,7 @@
         <v>204001</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1705,10 +1753,10 @@
         <v>1132</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>30</v>
@@ -1717,7 +1765,7 @@
         <v>204002</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1725,10 +1773,10 @@
         <v>1133</v>
       </c>
       <c r="B30" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>30</v>
@@ -1737,7 +1785,7 @@
         <v>204003</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1745,10 +1793,10 @@
         <v>1134</v>
       </c>
       <c r="B31" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C31" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>30</v>
@@ -1757,7 +1805,7 @@
         <v>204004</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1765,10 +1813,10 @@
         <v>1141</v>
       </c>
       <c r="B32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>30</v>
@@ -1777,7 +1825,7 @@
         <v>205001</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1785,10 +1833,10 @@
         <v>1142</v>
       </c>
       <c r="B33" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C33" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>30</v>
@@ -1797,7 +1845,7 @@
         <v>205002</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1805,10 +1853,10 @@
         <v>1143</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C34" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>30</v>
@@ -1817,7 +1865,7 @@
         <v>205003</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1825,10 +1873,10 @@
         <v>1144</v>
       </c>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C35" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>30</v>
@@ -1837,7 +1885,7 @@
         <v>205004</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1845,19 +1893,19 @@
         <v>1201</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="D36" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E36" s="5">
         <v>101011</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1865,19 +1913,19 @@
         <v>1202</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E37" s="2">
         <v>101021</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1885,19 +1933,19 @@
         <v>1203</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E38">
         <v>102011</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1905,19 +1953,19 @@
         <v>1204</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E39">
         <v>102012</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -1925,19 +1973,19 @@
         <v>1205</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E40">
         <v>102013</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1945,19 +1993,19 @@
         <v>1206</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E41">
         <v>102021</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1965,19 +2013,19 @@
         <v>1207</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E42">
         <v>102022</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1985,19 +2033,19 @@
         <v>1208</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E43">
         <v>102023</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2005,19 +2053,19 @@
         <v>1209</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E44">
         <v>103011</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2025,19 +2073,19 @@
         <v>1210</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E45">
         <v>103012</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2045,19 +2093,19 @@
         <v>1211</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E46">
         <v>103013</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2065,19 +2113,19 @@
         <v>1212</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E47">
         <v>103021</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2085,19 +2133,19 @@
         <v>1213</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E48">
         <v>103022</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2105,19 +2153,19 @@
         <v>1214</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E49">
         <v>103023</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2125,19 +2173,19 @@
         <v>1215</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E50">
         <v>104011</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2145,19 +2193,19 @@
         <v>1216</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E51">
         <v>104012</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2165,19 +2213,19 @@
         <v>1217</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E52">
         <v>104013</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2185,19 +2233,19 @@
         <v>1218</v>
       </c>
       <c r="B53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E53">
         <v>104021</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2205,19 +2253,19 @@
         <v>1219</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E54">
         <v>104022</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2225,19 +2273,19 @@
         <v>1220</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E55">
         <v>104023</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2245,19 +2293,19 @@
         <v>1221</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E56">
         <v>105011</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2265,19 +2313,19 @@
         <v>1222</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E57">
         <v>105012</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2285,19 +2333,19 @@
         <v>1223</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E58">
         <v>105013</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2305,19 +2353,19 @@
         <v>1224</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E59">
         <v>105021</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2325,19 +2373,19 @@
         <v>1225</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E60">
         <v>105022</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2345,19 +2393,19 @@
         <v>1226</v>
       </c>
       <c r="B61" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E61">
         <v>105023</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2365,19 +2413,19 @@
         <v>1227</v>
       </c>
       <c r="B62" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C62" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E62">
         <v>106011</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2385,19 +2433,19 @@
         <v>1228</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C63" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E63">
         <v>106012</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2405,19 +2453,19 @@
         <v>1229</v>
       </c>
       <c r="B64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E64">
         <v>106013</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2425,19 +2473,19 @@
         <v>1230</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E65">
         <v>106021</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2445,19 +2493,19 @@
         <v>1231</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C66" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E66">
         <v>106022</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2465,19 +2513,19 @@
         <v>1232</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E67">
         <v>106023</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2485,19 +2533,19 @@
         <v>1233</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E68">
         <v>107011</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2505,19 +2553,19 @@
         <v>1234</v>
       </c>
       <c r="B69" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C69" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E69">
         <v>107012</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2525,19 +2573,19 @@
         <v>1235</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C70" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E70">
         <v>107013</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2545,19 +2593,19 @@
         <v>1236</v>
       </c>
       <c r="B71" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C71" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E71">
         <v>107021</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -2565,19 +2613,19 @@
         <v>1237</v>
       </c>
       <c r="B72" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C72" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E72">
         <v>107022</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2585,19 +2633,19 @@
         <v>1238</v>
       </c>
       <c r="B73" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E73">
         <v>107023</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2605,19 +2653,19 @@
         <v>1301</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E74" s="5">
         <v>110001</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2625,19 +2673,19 @@
         <v>1302</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E75" s="2">
         <v>110002</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2645,19 +2693,19 @@
         <v>1303</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E76" s="5">
         <v>110003</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2665,19 +2713,19 @@
         <v>1304</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E77" s="2">
         <v>110004</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2685,19 +2733,19 @@
         <v>1305</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E78" s="5">
         <v>110005</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2705,19 +2753,19 @@
         <v>1306</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E79">
         <v>110006</v>
       </c>
       <c r="F79" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2725,19 +2773,19 @@
         <v>1307</v>
       </c>
       <c r="B80" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C80" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E80">
         <v>110007</v>
       </c>
       <c r="F80" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2745,19 +2793,19 @@
         <v>1401</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E81" s="2">
         <v>111001</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -2765,19 +2813,19 @@
         <v>1402</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E82" s="5">
         <v>111002</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -2785,19 +2833,19 @@
         <v>1403</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E83" s="2">
         <v>111003</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2805,19 +2853,19 @@
         <v>1404</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E84" s="5">
         <v>111004</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2825,19 +2873,19 @@
         <v>1405</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E85" s="8">
         <v>111005</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -2845,19 +2893,19 @@
         <v>1406</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E86" s="8">
         <v>111006</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -2865,19 +2913,19 @@
         <v>1407</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E87" s="8">
         <v>111007</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -2885,19 +2933,19 @@
         <v>1501</v>
       </c>
       <c r="B88" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C88" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E88">
         <v>113001</v>
       </c>
       <c r="F88" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2905,19 +2953,19 @@
         <v>1502</v>
       </c>
       <c r="B89" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E89">
         <v>113002</v>
       </c>
       <c r="F89" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2925,19 +2973,19 @@
         <v>1503</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C90" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E90">
         <v>113003</v>
       </c>
       <c r="F90" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -2945,19 +2993,19 @@
         <v>1504</v>
       </c>
       <c r="B91" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C91" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E91">
         <v>113004</v>
       </c>
       <c r="F91" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2965,19 +3013,19 @@
         <v>1505</v>
       </c>
       <c r="B92" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C92" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E92">
         <v>113005</v>
       </c>
       <c r="F92" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -2985,19 +3033,19 @@
         <v>1506</v>
       </c>
       <c r="B93" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C93" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E93">
         <v>113006</v>
       </c>
       <c r="F93" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3005,19 +3053,19 @@
         <v>1507</v>
       </c>
       <c r="B94" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C94" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E94">
         <v>113007</v>
       </c>
       <c r="F94" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -722,59 +722,59 @@
     <t>YellowEngine_4</t>
   </si>
   <si>
-    <t>Ingots_C1_128_5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C4_128_7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C4_128_6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ore_Rocks_Minerals_C2_128.png_9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ore_Rocks_Minerals_C2_128.png_35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ore_Rocks_Minerals_C3_128.png_44</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ore_Rocks_Minerals_C3_128.png_46</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C2_128_56</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ore_Rocks_Minerals_C2_128.png_23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ore_Rocks_Minerals_C2_128.png_32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ore_Rocks_Minerals_C3_128.png_50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C1_128_9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C1_128_31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C4_128_56</t>
+    <t>Ore_Rocks_Minerals_C3_128[Ore_Rocks_Minerals_C3_128.png_44]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128[Ore_Rocks_Minerals_C2_128.png_23]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128[Ore_Rocks_Minerals_C2_128.png_32]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C3_128[Ore_Rocks_Minerals_C3_128.png_46]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C3_128[Ore_Rocks_Minerals_C3_128.png_50]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128[Ore_Rocks_Minerals_C2_128.png_9]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128[Ore_Rocks_Minerals_C2_128.png_35]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C2_128[Ingots_C2_128_56]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128[Ingots_C4_128_6]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128[Ingots_C4_128_7]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C1_128[Ingots_C1_128_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C1_128[Ingots_C1_128_9]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C1_128[Ingots_C1_128_31]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128[Ingots_C4_128_56]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1227,7 +1227,7 @@
     <col min="2" max="2" width="17.875" customWidth="1"/>
     <col min="3" max="3" width="18.125" customWidth="1"/>
     <col min="4" max="5" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="35.75" customWidth="1"/>
+    <col min="6" max="6" width="64.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1298,7 +1298,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1315,7 +1315,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1332,7 +1332,7 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1349,7 +1349,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1366,7 +1366,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1383,7 +1383,7 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1400,7 +1400,7 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1434,7 +1434,7 @@
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1468,7 +1468,7 @@
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="214">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -722,6 +722,38 @@
     <t>YellowEngine_4</t>
   </si>
   <si>
+    <t>Ingots_C2_128[Ingots_C2_128_56]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128[Ingots_C4_128_6]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128[Ingots_C4_128_7]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C1_128[Ingots_C1_128_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C1_128[Ingots_C1_128_9]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C1_128[Ingots_C1_128_31]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingots_C4_128[Ingots_C4_128_56]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ore_Rocks_Minerals_C2_128[Ore_Rocks_Minerals_C2_128_35]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Ore_Rocks_Minerals_C3_128[Ore_Rocks_Minerals_C3_128.png_44]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -747,34 +779,6 @@
   </si>
   <si>
     <t>Ore_Rocks_Minerals_C2_128[Ore_Rocks_Minerals_C2_128.png_35]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C2_128[Ingots_C2_128_56]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C4_128[Ingots_C4_128_6]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C4_128[Ingots_C4_128_7]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C1_128[Ingots_C1_128_5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C1_128[Ingots_C1_128_9]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C1_128[Ingots_C1_128_31]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingots_C4_128[Ingots_C4_128_56]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1264,7 +1268,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1281,7 +1285,7 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1298,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1315,7 +1319,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1332,7 +1336,7 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1349,7 +1353,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1366,7 +1370,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1383,7 +1387,7 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1400,7 +1404,7 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1417,7 +1421,7 @@
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1434,7 +1438,7 @@
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1451,7 +1455,7 @@
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1468,7 +1472,7 @@
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1485,7 +1489,7 @@
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05903462-5B7C-4101-BF94-D2CBEFE6DB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="6195" windowHeight="14790"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="243">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -750,10 +751,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Ore_Rocks_Minerals_C2_128[Ore_Rocks_Minerals_C2_128_35]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Ore_Rocks_Minerals_C3_128[Ore_Rocks_Minerals_C3_128.png_44]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -780,12 +777,102 @@
   <si>
     <t>Ore_Rocks_Minerals_C2_128[Ore_Rocks_Minerals_C2_128.png_35]</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreenEngine_5</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>GreenEngine_6</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>GreenEngine_7</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>RedEngine_5</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>RedEngine_6</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>RedEngine_7</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>BlueEngine_5</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>BlueEngine_6</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>BlueEngine_7</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>PurpleEngine_5</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>PurpleEngine_6</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>PurpleEngine_7</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>YellowEngine_5</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>YellowEngine_6</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>YellowEngine_7</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -903,31 +990,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -948,15 +1035,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F94" totalsRowShown="0">
-  <autoFilter ref="A1:F94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:F109" totalsRowShown="0">
+  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="4" name="Name"/>
-    <tableColumn id="2" name="DisplayName"/>
-    <tableColumn id="5" name="ItemType"/>
-    <tableColumn id="6" name="EntityId"/>
-    <tableColumn id="3" name="ItemIcon"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ItemType"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EntityId"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ItemIcon"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1224,8 +1311,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.875" customWidth="1"/>
@@ -1268,7 +1355,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1302,7 +1389,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1336,7 +1423,7 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1370,7 +1457,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1404,7 +1491,7 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1438,7 +1525,7 @@
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1472,7 +1559,7 @@
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1574,39 +1661,39 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>213</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>202001</v>
+        <v>201005</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>1112</v>
+      <c r="A21" s="1">
+        <v>1106</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>202002</v>
+        <v>201006</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>31</v>
@@ -1614,19 +1701,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>202003</v>
+        <v>201007</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>31</v>
@@ -1634,19 +1721,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="B23" t="s">
-        <v>186</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E23">
-        <v>202004</v>
+        <v>202001</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>31</v>
@@ -1654,19 +1741,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>174</v>
+        <v>28</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>203001</v>
+        <v>202002</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>31</v>
@@ -1674,19 +1761,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
-        <v>1122</v>
+        <v>1113</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>203002</v>
+        <v>202003</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>31</v>
@@ -1694,19 +1781,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
-        <v>1123</v>
+        <v>1114</v>
       </c>
       <c r="B26" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>203003</v>
+        <v>202004</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>31</v>
@@ -1714,19 +1801,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>1124</v>
+        <v>1115</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="C27" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>203004</v>
+        <v>202005</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>31</v>
@@ -1734,19 +1821,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
-        <v>1131</v>
+        <v>1116</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>204001</v>
+        <v>202006</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>31</v>
@@ -1754,19 +1841,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>1132</v>
+        <v>1117</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="C29" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E29">
-        <v>204002</v>
+        <v>202007</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>31</v>
@@ -1774,19 +1861,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="B30" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C30" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>204003</v>
+        <v>203001</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>31</v>
@@ -1794,19 +1881,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C31" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E31">
-        <v>204004</v>
+        <v>203002</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>31</v>
@@ -1814,19 +1901,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
-        <v>1141</v>
+        <v>1123</v>
       </c>
       <c r="B32" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C32" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E32">
-        <v>205001</v>
+        <v>203003</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>31</v>
@@ -1834,19 +1921,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
-        <v>1142</v>
+        <v>1124</v>
       </c>
       <c r="B33" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C33" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E33">
-        <v>205002</v>
+        <v>203004</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>31</v>
@@ -1854,19 +1941,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
-        <v>1143</v>
+        <v>1125</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C34" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>205003</v>
+        <v>203005</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>31</v>
@@ -1874,19 +1961,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>1144</v>
+        <v>1126</v>
       </c>
       <c r="B35" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="C35" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E35">
-        <v>205004</v>
+        <v>203006</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>31</v>
@@ -1894,19 +1981,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>1201</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>34</v>
+        <v>1127</v>
+      </c>
+      <c r="B36" t="s">
+        <v>229</v>
+      </c>
+      <c r="C36" t="s">
+        <v>230</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="5">
-        <v>101011</v>
+        <v>30</v>
+      </c>
+      <c r="E36">
+        <v>203007</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>31</v>
@@ -1914,319 +2001,319 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <v>1202</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="2">
-        <v>101021</v>
-      </c>
-      <c r="F37" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>191</v>
+      </c>
+      <c r="C37" t="s">
+        <v>178</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37">
+        <v>204001</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <v>1203</v>
+        <v>1132</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>36</v>
+        <v>179</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E38">
-        <v>102011</v>
-      </c>
-      <c r="F38" s="3" t="s">
+        <v>204002</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <v>1204</v>
+        <v>1133</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>36</v>
+        <v>180</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E39">
-        <v>102012</v>
-      </c>
-      <c r="F39" s="3" t="s">
+        <v>204003</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
-        <v>1205</v>
+        <v>1134</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>181</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E40">
-        <v>102013</v>
-      </c>
-      <c r="F40" s="3" t="s">
+        <v>204004</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
-        <v>1206</v>
+        <v>1135</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>36</v>
+        <v>232</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E41">
-        <v>102021</v>
-      </c>
-      <c r="F41" s="3" t="s">
+        <v>204005</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
-        <v>1207</v>
+        <v>1136</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>36</v>
+        <v>234</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E42">
-        <v>102022</v>
-      </c>
-      <c r="F42" s="3" t="s">
+        <v>204006</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
-        <v>1208</v>
+        <v>1137</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>36</v>
+        <v>236</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E43">
-        <v>102023</v>
-      </c>
-      <c r="F43" s="3" t="s">
+        <v>204007</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
-        <v>1209</v>
+        <v>1141</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="C44" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>36</v>
+        <v>182</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E44">
-        <v>103011</v>
-      </c>
-      <c r="F44" s="3" t="s">
+        <v>205001</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
-        <v>1210</v>
+        <v>1142</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>36</v>
+        <v>183</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E45">
-        <v>103012</v>
-      </c>
-      <c r="F45" s="3" t="s">
+        <v>205002</v>
+      </c>
+      <c r="F45" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
-        <v>1211</v>
+        <v>1143</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>36</v>
+        <v>184</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E46">
-        <v>103013</v>
-      </c>
-      <c r="F46" s="3" t="s">
+        <v>205003</v>
+      </c>
+      <c r="F46" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
-        <v>1212</v>
+        <v>1144</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>198</v>
       </c>
       <c r="C47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>36</v>
+        <v>185</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E47">
-        <v>103021</v>
-      </c>
-      <c r="F47" s="3" t="s">
+        <v>205004</v>
+      </c>
+      <c r="F47" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
-        <v>1213</v>
+        <v>1145</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>36</v>
+        <v>238</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E48">
-        <v>103022</v>
-      </c>
-      <c r="F48" s="3" t="s">
+        <v>205005</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
-        <v>1214</v>
+        <v>1146</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>239</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>36</v>
+        <v>240</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E49">
-        <v>103023</v>
-      </c>
-      <c r="F49" s="3" t="s">
+        <v>205006</v>
+      </c>
+      <c r="F49" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
-        <v>1215</v>
+        <v>1147</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>241</v>
       </c>
       <c r="C50" t="s">
-        <v>160</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>36</v>
+        <v>242</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E50">
-        <v>104011</v>
-      </c>
-      <c r="F50" s="3" t="s">
+        <v>205007</v>
+      </c>
+      <c r="F50" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
-        <v>1216</v>
-      </c>
-      <c r="B51" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E51">
-        <v>104012</v>
-      </c>
-      <c r="F51" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="5">
+        <v>101011</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
-        <v>1217</v>
-      </c>
-      <c r="B52" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" t="s">
-        <v>120</v>
+        <v>1202</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E52">
-        <v>104013</v>
+      <c r="E52" s="2">
+        <v>101021</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>31</v>
@@ -2234,19 +2321,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
-        <v>1218</v>
+        <v>1203</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E53">
-        <v>104021</v>
+        <v>102011</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>31</v>
@@ -2254,19 +2341,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
-        <v>1219</v>
+        <v>1204</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="C54" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E54">
-        <v>104022</v>
+        <v>102012</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>31</v>
@@ -2274,19 +2361,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
-        <v>1220</v>
+        <v>1205</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E55">
-        <v>104023</v>
+        <v>102013</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>31</v>
@@ -2294,19 +2381,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
-        <v>1221</v>
+        <v>1206</v>
       </c>
       <c r="B56" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E56">
-        <v>105011</v>
+        <v>102021</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>31</v>
@@ -2314,19 +2401,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
-        <v>1222</v>
+        <v>1207</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E57">
-        <v>105012</v>
+        <v>102022</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>31</v>
@@ -2334,19 +2421,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
-        <v>1223</v>
+        <v>1208</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E58">
-        <v>105013</v>
+        <v>102023</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>31</v>
@@ -2354,19 +2441,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
-        <v>1224</v>
+        <v>1209</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="C59" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E59">
-        <v>105021</v>
+        <v>103011</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>31</v>
@@ -2374,19 +2461,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
-        <v>1225</v>
+        <v>1210</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E60">
-        <v>105022</v>
+        <v>103012</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>31</v>
@@ -2394,19 +2481,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
-        <v>1226</v>
+        <v>1211</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="C61" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E61">
-        <v>105023</v>
+        <v>103013</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>31</v>
@@ -2414,19 +2501,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
-        <v>1227</v>
+        <v>1212</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="C62" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E62">
-        <v>106011</v>
+        <v>103021</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>31</v>
@@ -2434,19 +2521,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
-        <v>1228</v>
+        <v>1213</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E63">
-        <v>106012</v>
+        <v>103022</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>31</v>
@@ -2454,19 +2541,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
-        <v>1229</v>
+        <v>1214</v>
       </c>
       <c r="B64" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="C64" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E64">
-        <v>106013</v>
+        <v>103023</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>31</v>
@@ -2474,19 +2561,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
-        <v>1230</v>
+        <v>1215</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C65" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E65">
-        <v>106021</v>
+        <v>104011</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>31</v>
@@ -2494,19 +2581,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
-        <v>1231</v>
+        <v>1216</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C66" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E66">
-        <v>106022</v>
+        <v>104012</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>31</v>
@@ -2514,19 +2601,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
-        <v>1232</v>
+        <v>1217</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E67">
-        <v>106023</v>
+        <v>104013</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>31</v>
@@ -2534,19 +2621,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
-        <v>1233</v>
+        <v>1218</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E68">
-        <v>107011</v>
+        <v>104021</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>31</v>
@@ -2554,19 +2641,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
-        <v>1234</v>
+        <v>1219</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="C69" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E69">
-        <v>107012</v>
+        <v>104022</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>31</v>
@@ -2574,19 +2661,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="B70" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E70">
-        <v>107013</v>
+        <v>104023</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>31</v>
@@ -2594,19 +2681,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
-        <v>1236</v>
+        <v>1221</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E71">
-        <v>107021</v>
+        <v>105011</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>31</v>
@@ -2614,19 +2701,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
-        <v>1237</v>
+        <v>1222</v>
       </c>
       <c r="B72" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C72" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E72">
-        <v>107022</v>
+        <v>105012</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>31</v>
@@ -2634,19 +2721,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
-        <v>1238</v>
+        <v>1223</v>
       </c>
       <c r="B73" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E73">
-        <v>107023</v>
+        <v>105013</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>31</v>
@@ -2654,421 +2741,721 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
-        <v>1301</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E74" s="5">
-        <v>110001</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>57</v>
+        <v>1224</v>
+      </c>
+      <c r="B74" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E74">
+        <v>105021</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
-        <v>1302</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>39</v>
+      <c r="A75" s="4">
+        <v>1225</v>
+      </c>
+      <c r="B75" t="s">
+        <v>133</v>
+      </c>
+      <c r="C75" t="s">
+        <v>134</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E75" s="2">
-        <v>110002</v>
+      <c r="E75">
+        <v>105022</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
-        <v>1303</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E76" s="5">
-        <v>110003</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>57</v>
+        <v>1226</v>
+      </c>
+      <c r="B76" t="s">
+        <v>135</v>
+      </c>
+      <c r="C76" t="s">
+        <v>136</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E76">
+        <v>105023</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
-        <v>1304</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>41</v>
+      <c r="A77" s="4">
+        <v>1227</v>
+      </c>
+      <c r="B77" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" t="s">
+        <v>155</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E77" s="2">
-        <v>110004</v>
+      <c r="E77">
+        <v>106011</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
-        <v>1305</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E78" s="5">
-        <v>110005</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>57</v>
+        <v>1228</v>
+      </c>
+      <c r="B78" t="s">
+        <v>137</v>
+      </c>
+      <c r="C78" t="s">
+        <v>138</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E78">
+        <v>106012</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>1306</v>
+      <c r="A79" s="4">
+        <v>1229</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
-      </c>
-      <c r="D79" t="s">
+        <v>140</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E79">
-        <v>110006</v>
-      </c>
-      <c r="F79" t="s">
-        <v>57</v>
+        <v>106013</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>1307</v>
+      <c r="A80" s="4">
+        <v>1230</v>
       </c>
       <c r="B80" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="C80" t="s">
-        <v>98</v>
-      </c>
-      <c r="D80" t="s">
+        <v>163</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E80">
-        <v>110007</v>
-      </c>
-      <c r="F80" t="s">
-        <v>57</v>
+        <v>106021</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
-        <v>1401</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>48</v>
+      <c r="A81" s="4">
+        <v>1231</v>
+      </c>
+      <c r="B81" t="s">
+        <v>142</v>
+      </c>
+      <c r="C81" t="s">
+        <v>143</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E81" s="2">
-        <v>111001</v>
+      <c r="E81">
+        <v>106022</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
-        <v>1402</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E82" s="5">
-        <v>111002</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>58</v>
+        <v>1232</v>
+      </c>
+      <c r="B82" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82" t="s">
+        <v>145</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E82">
+        <v>106023</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
-        <v>1403</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>54</v>
+      <c r="A83" s="4">
+        <v>1233</v>
+      </c>
+      <c r="B83" t="s">
+        <v>146</v>
+      </c>
+      <c r="C83" t="s">
+        <v>156</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E83" s="2">
-        <v>111003</v>
+      <c r="E83">
+        <v>107011</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
-        <v>1404</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E84" s="5">
-        <v>111004</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>58</v>
+        <v>1234</v>
+      </c>
+      <c r="B84" t="s">
+        <v>147</v>
+      </c>
+      <c r="C84" t="s">
+        <v>148</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E84">
+        <v>107012</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="7">
-        <v>1405</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E85" s="8">
-        <v>111005</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>58</v>
+      <c r="A85" s="4">
+        <v>1235</v>
+      </c>
+      <c r="B85" t="s">
+        <v>164</v>
+      </c>
+      <c r="C85" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E85">
+        <v>107013</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="7">
-        <v>1406</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E86" s="8">
-        <v>111006</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>58</v>
+      <c r="A86" s="4">
+        <v>1236</v>
+      </c>
+      <c r="B86" t="s">
+        <v>149</v>
+      </c>
+      <c r="C86" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E86">
+        <v>107021</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="7">
-        <v>1407</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E87" s="8">
-        <v>111007</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>58</v>
+      <c r="A87" s="4">
+        <v>1237</v>
+      </c>
+      <c r="B87" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" t="s">
+        <v>151</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E87">
+        <v>107022</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>1501</v>
+      <c r="A88" s="4">
+        <v>1238</v>
       </c>
       <c r="B88" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
-      </c>
-      <c r="D88" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E88">
-        <v>113001</v>
-      </c>
-      <c r="F88" t="s">
-        <v>166</v>
+        <v>107023</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>1502</v>
-      </c>
-      <c r="B89" t="s">
-        <v>104</v>
-      </c>
-      <c r="C89" t="s">
-        <v>105</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E89">
-        <v>113002</v>
-      </c>
-      <c r="F89" t="s">
-        <v>166</v>
+      <c r="A89" s="4">
+        <v>1301</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E89" s="5">
+        <v>110001</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>1503</v>
-      </c>
-      <c r="B90" t="s">
-        <v>106</v>
-      </c>
-      <c r="C90" t="s">
-        <v>107</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E90">
-        <v>113003</v>
-      </c>
-      <c r="F90" t="s">
-        <v>166</v>
+      <c r="A90" s="1">
+        <v>1302</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E90" s="2">
+        <v>110002</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>1504</v>
-      </c>
-      <c r="B91" t="s">
-        <v>108</v>
-      </c>
-      <c r="C91" t="s">
-        <v>109</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E91">
-        <v>113004</v>
-      </c>
-      <c r="F91" t="s">
-        <v>166</v>
+      <c r="A91" s="4">
+        <v>1303</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E91" s="5">
+        <v>110003</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>1505</v>
-      </c>
-      <c r="B92" t="s">
-        <v>110</v>
-      </c>
-      <c r="C92" t="s">
-        <v>111</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E92">
-        <v>113005</v>
-      </c>
-      <c r="F92" t="s">
-        <v>166</v>
+      <c r="A92" s="1">
+        <v>1304</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E92" s="2">
+        <v>110004</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>1506</v>
-      </c>
-      <c r="B93" t="s">
-        <v>112</v>
-      </c>
-      <c r="C93" t="s">
-        <v>113</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E93">
-        <v>113006</v>
-      </c>
-      <c r="F93" t="s">
-        <v>166</v>
+      <c r="A93" s="4">
+        <v>1305</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E93" s="5">
+        <v>110005</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
+        <v>1306</v>
+      </c>
+      <c r="B94" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94" t="s">
+        <v>96</v>
+      </c>
+      <c r="D94" t="s">
+        <v>36</v>
+      </c>
+      <c r="E94">
+        <v>110006</v>
+      </c>
+      <c r="F94" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>1307</v>
+      </c>
+      <c r="B95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C95" t="s">
+        <v>98</v>
+      </c>
+      <c r="D95" t="s">
+        <v>36</v>
+      </c>
+      <c r="E95">
+        <v>110007</v>
+      </c>
+      <c r="F95" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>1401</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E96" s="2">
+        <v>111001</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="4">
+        <v>1402</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E97" s="5">
+        <v>111002</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>1403</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E98" s="2">
+        <v>111003</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="4">
+        <v>1404</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E99" s="5">
+        <v>111004</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="7">
+        <v>1405</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E100" s="8">
+        <v>111005</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="7">
+        <v>1406</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E101" s="8">
+        <v>111006</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="7">
+        <v>1407</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E102" s="8">
+        <v>111007</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>1501</v>
+      </c>
+      <c r="B103" t="s">
+        <v>116</v>
+      </c>
+      <c r="C103" t="s">
+        <v>103</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E103">
+        <v>113001</v>
+      </c>
+      <c r="F103" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>1502</v>
+      </c>
+      <c r="B104" t="s">
+        <v>104</v>
+      </c>
+      <c r="C104" t="s">
+        <v>105</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E104">
+        <v>113002</v>
+      </c>
+      <c r="F104" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>1503</v>
+      </c>
+      <c r="B105" t="s">
+        <v>106</v>
+      </c>
+      <c r="C105" t="s">
+        <v>107</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E105">
+        <v>113003</v>
+      </c>
+      <c r="F105" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>1504</v>
+      </c>
+      <c r="B106" t="s">
+        <v>108</v>
+      </c>
+      <c r="C106" t="s">
+        <v>109</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E106">
+        <v>113004</v>
+      </c>
+      <c r="F106" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>1505</v>
+      </c>
+      <c r="B107" t="s">
+        <v>110</v>
+      </c>
+      <c r="C107" t="s">
+        <v>111</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107">
+        <v>113005</v>
+      </c>
+      <c r="F107" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>1506</v>
+      </c>
+      <c r="B108" t="s">
+        <v>112</v>
+      </c>
+      <c r="C108" t="s">
+        <v>113</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E108">
+        <v>113006</v>
+      </c>
+      <c r="F108" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109">
         <v>1507</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B109" t="s">
         <v>114</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C109" t="s">
         <v>115</v>
       </c>
-      <c r="D94" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E94">
+      <c r="D109" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E109">
         <v>113007</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F109" t="s">
         <v>166</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05903462-5B7C-4101-BF94-D2CBEFE6DB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="256">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -867,12 +866,64 @@
   </si>
   <si>
     <t>노랑 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>greenEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>greenEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blueEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blueEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blueEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purpleEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purpleEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purpleEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellowEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellowEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellowEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1035,15 +1086,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:F109" totalsRowShown="0">
-  <autoFilter ref="A1:F109" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:F109" totalsRowShown="0">
+  <autoFilter ref="A1:F109"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DisplayName"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ItemType"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EntityId"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ItemIcon"/>
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="4" name="Name"/>
+    <tableColumn id="2" name="DisplayName"/>
+    <tableColumn id="5" name="ItemType"/>
+    <tableColumn id="6" name="EntityId"/>
+    <tableColumn id="3" name="ItemIcon"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1311,7 +1362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1596,7 +1647,7 @@
         <v>201001</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>31</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1616,7 +1667,7 @@
         <v>201002</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>31</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1636,7 +1687,7 @@
         <v>201003</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>31</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1656,7 +1707,7 @@
         <v>201004</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>31</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1676,7 +1727,7 @@
         <v>201005</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>31</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1696,7 +1747,7 @@
         <v>201006</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>31</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1716,7 +1767,7 @@
         <v>201007</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>31</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1736,7 +1787,7 @@
         <v>202001</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1756,7 +1807,7 @@
         <v>202002</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>31</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1776,7 +1827,7 @@
         <v>202003</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1796,7 +1847,7 @@
         <v>202004</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>31</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1816,7 +1867,7 @@
         <v>202005</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>31</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1836,7 +1887,7 @@
         <v>202006</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>31</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1856,7 +1907,7 @@
         <v>202007</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1876,7 +1927,7 @@
         <v>203001</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>31</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1896,7 +1947,7 @@
         <v>203002</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>31</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1916,7 +1967,7 @@
         <v>203003</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>31</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1936,7 +1987,7 @@
         <v>203004</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>31</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1956,7 +2007,7 @@
         <v>203005</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>31</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1976,7 +2027,7 @@
         <v>203006</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>31</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1996,7 +2047,7 @@
         <v>203007</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>31</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2016,7 +2067,7 @@
         <v>204001</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>31</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2036,7 +2087,7 @@
         <v>204002</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>31</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2056,7 +2107,7 @@
         <v>204003</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>31</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2076,7 +2127,7 @@
         <v>204004</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>31</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2096,7 +2147,7 @@
         <v>204005</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>31</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2116,7 +2167,7 @@
         <v>204006</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>31</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2136,7 +2187,7 @@
         <v>204007</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>31</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2156,7 +2207,7 @@
         <v>205001</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>31</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2176,7 +2227,7 @@
         <v>205002</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>31</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2196,7 +2247,7 @@
         <v>205003</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>31</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2216,7 +2267,7 @@
         <v>205004</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>31</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2236,7 +2287,7 @@
         <v>205005</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>31</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2256,7 +2307,7 @@
         <v>205006</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>31</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2276,7 +2327,7 @@
         <v>205007</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>31</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">

--- a/Assets/100_Data/XlsxFiles/Item_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Item_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="277">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,10 +144,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>stone_miner1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -232,14 +228,6 @@
     <t>엔진 합성기 Lv.5</t>
   </si>
   <si>
-    <t>labIcon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>engineMergerIcon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Obsidian_Material</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -611,10 +599,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>resourceMergerIcon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GreenEngine_4</t>
   </si>
   <si>
@@ -917,6 +901,106 @@
   </si>
   <si>
     <t>yellowEngine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource_merger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource_merger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_merger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_merger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laboratory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copper_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iron_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsidian_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tunstein_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>titanium_processor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -955,7 +1039,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1020,24 +1104,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1045,9 +1118,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -1063,9 +1133,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1386,7 +1453,7 @@
         <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -1406,7 +1473,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1423,7 +1490,7 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1440,7 +1507,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1457,7 +1524,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1474,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1491,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1508,7 +1575,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1525,7 +1592,7 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1533,16 +1600,16 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1550,16 +1617,16 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1567,16 +1634,16 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1584,16 +1651,16 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1601,16 +1668,16 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1618,36 +1685,36 @@
         <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>1101</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
-      </c>
-      <c r="D16" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E16">
         <v>201001</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>243</v>
+      <c r="F16" s="5" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1658,76 +1725,76 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D17" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E17">
         <v>201002</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>243</v>
+      <c r="F17" s="5" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>1103</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
-      </c>
-      <c r="D18" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E18">
         <v>201003</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>243</v>
+      <c r="F18" s="5" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>1104</v>
       </c>
       <c r="B19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" t="s">
         <v>167</v>
       </c>
-      <c r="C19" t="s">
-        <v>171</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E19">
         <v>201004</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>244</v>
+      <c r="F19" s="5" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>1105</v>
       </c>
       <c r="B20" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E20">
         <v>201005</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>244</v>
+      <c r="F20" s="5" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1735,63 +1802,63 @@
         <v>1106</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C21" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E21">
         <v>201006</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>244</v>
+      <c r="F21" s="5" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>1107</v>
       </c>
       <c r="B22" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E22">
         <v>201007</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>244</v>
+      <c r="F22" s="5" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>1111</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
-      </c>
-      <c r="D23" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E23">
         <v>202001</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>245</v>
+      <c r="F23" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>1112</v>
       </c>
       <c r="B24" t="s">
@@ -1800,18 +1867,18 @@
       <c r="C24" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E24">
         <v>202002</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>246</v>
+      <c r="F24" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>1113</v>
       </c>
       <c r="B25" t="s">
@@ -1820,1294 +1887,1294 @@
       <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E25">
         <v>202003</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>245</v>
+      <c r="F25" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>1114</v>
       </c>
       <c r="B26" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>173</v>
-      </c>
-      <c r="D26" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E26">
         <v>202004</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>246</v>
+      <c r="F26" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>1115</v>
       </c>
       <c r="B27" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s">
-        <v>220</v>
-      </c>
-      <c r="D27" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E27">
         <v>202005</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>246</v>
+      <c r="F27" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>1116</v>
       </c>
       <c r="B28" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C28" t="s">
-        <v>222</v>
-      </c>
-      <c r="D28" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E28">
         <v>202006</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>246</v>
+      <c r="F28" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29" s="3">
         <v>1117</v>
       </c>
       <c r="B29" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C29" t="s">
-        <v>224</v>
-      </c>
-      <c r="D29" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E29">
         <v>202007</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>245</v>
+      <c r="F29" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="A30" s="3">
         <v>1121</v>
       </c>
       <c r="B30" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
-      </c>
-      <c r="D30" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E30">
         <v>203001</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>247</v>
+      <c r="F30" s="5" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
         <v>1122</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C31" t="s">
-        <v>175</v>
-      </c>
-      <c r="D31" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E31">
         <v>203002</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>247</v>
+      <c r="F31" s="5" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
         <v>1123</v>
       </c>
       <c r="B32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C32" t="s">
-        <v>176</v>
-      </c>
-      <c r="D32" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E32">
         <v>203003</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>248</v>
+      <c r="F32" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
         <v>1124</v>
       </c>
       <c r="B33" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C33" t="s">
-        <v>177</v>
-      </c>
-      <c r="D33" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E33">
         <v>203004</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>248</v>
+      <c r="F33" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
         <v>1125</v>
       </c>
       <c r="B34" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C34" t="s">
-        <v>226</v>
-      </c>
-      <c r="D34" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E34">
         <v>203005</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>248</v>
+      <c r="F34" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+      <c r="A35" s="3">
         <v>1126</v>
       </c>
       <c r="B35" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C35" t="s">
-        <v>228</v>
-      </c>
-      <c r="D35" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E35">
         <v>203006</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>248</v>
+      <c r="F35" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+      <c r="A36" s="3">
         <v>1127</v>
       </c>
       <c r="B36" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C36" t="s">
-        <v>230</v>
-      </c>
-      <c r="D36" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E36">
         <v>203007</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>249</v>
+      <c r="F36" s="5" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+      <c r="A37" s="3">
         <v>1131</v>
       </c>
       <c r="B37" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D37" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E37">
         <v>204001</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>250</v>
+      <c r="F37" s="5" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
         <v>1132</v>
       </c>
       <c r="B38" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C38" t="s">
-        <v>179</v>
-      </c>
-      <c r="D38" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E38">
         <v>204002</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>251</v>
+      <c r="F38" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+      <c r="A39" s="3">
         <v>1133</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D39" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E39">
         <v>204003</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>250</v>
+      <c r="F39" s="5" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="A40" s="3">
         <v>1134</v>
       </c>
       <c r="B40" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C40" t="s">
-        <v>181</v>
-      </c>
-      <c r="D40" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E40">
         <v>204004</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>252</v>
+      <c r="F40" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="4">
+      <c r="A41" s="3">
         <v>1135</v>
       </c>
       <c r="B41" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
-      </c>
-      <c r="D41" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E41">
         <v>204005</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>251</v>
+      <c r="F41" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="A42" s="3">
         <v>1136</v>
       </c>
       <c r="B42" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C42" t="s">
-        <v>234</v>
-      </c>
-      <c r="D42" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E42">
         <v>204006</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>251</v>
+      <c r="F42" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="4">
+      <c r="A43" s="3">
         <v>1137</v>
       </c>
       <c r="B43" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C43" t="s">
-        <v>236</v>
-      </c>
-      <c r="D43" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E43">
         <v>204007</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>250</v>
+      <c r="F43" s="5" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
+      <c r="A44" s="3">
         <v>1141</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C44" t="s">
-        <v>182</v>
-      </c>
-      <c r="D44" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E44">
         <v>205001</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>253</v>
+      <c r="F44" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
+      <c r="A45" s="3">
         <v>1142</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>183</v>
-      </c>
-      <c r="D45" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E45">
         <v>205002</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>254</v>
+      <c r="F45" s="5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
+      <c r="A46" s="3">
         <v>1143</v>
       </c>
       <c r="B46" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C46" t="s">
-        <v>184</v>
-      </c>
-      <c r="D46" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E46">
         <v>205003</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>255</v>
+      <c r="F46" s="5" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+      <c r="A47" s="3">
         <v>1144</v>
       </c>
       <c r="B47" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C47" t="s">
-        <v>185</v>
-      </c>
-      <c r="D47" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E47">
         <v>205004</v>
       </c>
-      <c r="F47" s="6" t="s">
-        <v>254</v>
+      <c r="F47" s="5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+      <c r="A48" s="3">
         <v>1145</v>
       </c>
       <c r="B48" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C48" t="s">
-        <v>238</v>
-      </c>
-      <c r="D48" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E48">
         <v>205005</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>253</v>
+      <c r="F48" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
+      <c r="A49" s="3">
         <v>1146</v>
       </c>
       <c r="B49" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C49" t="s">
-        <v>240</v>
-      </c>
-      <c r="D49" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E49">
         <v>205006</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>254</v>
+      <c r="F49" s="5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+      <c r="A50" s="3">
         <v>1147</v>
       </c>
       <c r="B50" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>242</v>
-      </c>
-      <c r="D50" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E50">
         <v>205007</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>254</v>
+      <c r="F50" s="5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+      <c r="A51" s="3">
         <v>1201</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="4">
+        <v>101011</v>
+      </c>
+      <c r="F51" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>1202</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C52" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E51" s="5">
-        <v>101011</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
-        <v>1202</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52" s="2">
         <v>101021</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>31</v>
+      <c r="F52" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+      <c r="A53" s="3">
         <v>1203</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E53">
         <v>102011</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>31</v>
+      <c r="F53" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
+      <c r="A54" s="3">
         <v>1204</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54">
         <v>102012</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>31</v>
+      <c r="F54" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
+      <c r="A55" s="3">
         <v>1205</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55">
         <v>102013</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>31</v>
+      <c r="F55" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+      <c r="A56" s="3">
         <v>1206</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E56">
         <v>102021</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>31</v>
+      <c r="F56" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="4">
+      <c r="A57" s="3">
         <v>1207</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E57">
         <v>102022</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>31</v>
+      <c r="F57" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
+      <c r="A58" s="3">
         <v>1208</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E58">
         <v>102023</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>31</v>
+      <c r="F58" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+      <c r="A59" s="3">
         <v>1209</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59">
         <v>103011</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>31</v>
+      <c r="F59" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="4">
+      <c r="A60" s="3">
         <v>1210</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E60">
         <v>103012</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>31</v>
+      <c r="F60" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="4">
+      <c r="A61" s="3">
         <v>1211</v>
       </c>
       <c r="B61" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C61" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E61">
         <v>103013</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>31</v>
+      <c r="F61" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="4">
+      <c r="A62" s="3">
         <v>1212</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E62">
         <v>103021</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>31</v>
+      <c r="F62" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+      <c r="A63" s="3">
         <v>1213</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E63">
         <v>103022</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>31</v>
+      <c r="F63" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
+      <c r="A64" s="3">
         <v>1214</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E64">
         <v>103023</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>31</v>
+      <c r="F64" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
+      <c r="A65" s="3">
         <v>1215</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C65" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E65">
         <v>104011</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>31</v>
+      <c r="F65" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
+      <c r="A66" s="3">
         <v>1216</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C66" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E66">
         <v>104012</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>31</v>
+      <c r="F66" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
+      <c r="A67" s="3">
         <v>1217</v>
       </c>
       <c r="B67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C67" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E67">
         <v>104013</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>31</v>
+      <c r="F67" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="4">
+      <c r="A68" s="3">
         <v>1218</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C68" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E68">
         <v>104021</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>31</v>
+      <c r="F68" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="4">
+      <c r="A69" s="3">
         <v>1219</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E69">
         <v>104022</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>31</v>
+      <c r="F69" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="4">
+      <c r="A70" s="3">
         <v>1220</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E70">
         <v>104023</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>31</v>
+      <c r="F70" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="4">
+      <c r="A71" s="3">
         <v>1221</v>
       </c>
       <c r="B71" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C71" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E71">
         <v>105011</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>31</v>
+      <c r="F71" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="4">
+      <c r="A72" s="3">
         <v>1222</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E72">
         <v>105012</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>31</v>
+      <c r="F72" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="4">
+      <c r="A73" s="3">
         <v>1223</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C73" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E73">
         <v>105013</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>31</v>
+      <c r="F73" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="4">
+      <c r="A74" s="3">
         <v>1224</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C74" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E74">
         <v>105021</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>31</v>
+      <c r="F74" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="4">
+      <c r="A75" s="3">
         <v>1225</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C75" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E75">
         <v>105022</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>31</v>
+      <c r="F75" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="4">
+      <c r="A76" s="3">
         <v>1226</v>
       </c>
       <c r="B76" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E76">
         <v>105023</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>31</v>
+      <c r="F76" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="4">
+      <c r="A77" s="3">
         <v>1227</v>
       </c>
       <c r="B77" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E77">
         <v>106011</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>31</v>
+      <c r="F77" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="4">
+      <c r="A78" s="3">
         <v>1228</v>
       </c>
       <c r="B78" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C78" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E78">
         <v>106012</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>31</v>
+      <c r="F78" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="4">
+      <c r="A79" s="3">
         <v>1229</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C79" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E79">
         <v>106013</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>31</v>
+      <c r="F79" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="4">
+      <c r="A80" s="3">
         <v>1230</v>
       </c>
       <c r="B80" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E80">
         <v>106021</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>31</v>
+      <c r="F80" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="4">
+      <c r="A81" s="3">
         <v>1231</v>
       </c>
       <c r="B81" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C81" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E81">
         <v>106022</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>31</v>
+      <c r="F81" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="4">
+      <c r="A82" s="3">
         <v>1232</v>
       </c>
       <c r="B82" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C82" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E82">
         <v>106023</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>31</v>
+      <c r="F82" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="4">
+      <c r="A83" s="3">
         <v>1233</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C83" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E83">
         <v>107011</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>31</v>
+      <c r="F83" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="4">
+      <c r="A84" s="3">
         <v>1234</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E84">
         <v>107012</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>31</v>
+      <c r="F84" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="4">
+      <c r="A85" s="3">
         <v>1235</v>
       </c>
       <c r="B85" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C85" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E85">
         <v>107013</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>31</v>
+      <c r="F85" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="4">
+      <c r="A86" s="3">
         <v>1236</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C86" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E86">
         <v>107021</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>31</v>
+      <c r="F86" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="4">
+      <c r="A87" s="3">
         <v>1237</v>
       </c>
       <c r="B87" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E87">
         <v>107022</v>
       </c>
-      <c r="F87" s="3" t="s">
-        <v>31</v>
+      <c r="F87" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="4">
+      <c r="A88" s="3">
         <v>1238</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C88" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E88">
         <v>107023</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>31</v>
+      <c r="F88" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="4">
+      <c r="A89" s="3">
         <v>1301</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E89" s="5">
+      <c r="D89" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="4">
         <v>110001</v>
       </c>
-      <c r="F89" s="6" t="s">
-        <v>57</v>
+      <c r="F89" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -3115,39 +3182,39 @@
         <v>1302</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E90" s="2">
         <v>110002</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>57</v>
+      <c r="F90" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="4">
+      <c r="A91" s="3">
         <v>1303</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E91" s="5">
+      <c r="B91" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="4">
         <v>110003</v>
       </c>
-      <c r="F91" s="6" t="s">
-        <v>57</v>
+      <c r="F91" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3155,39 +3222,39 @@
         <v>1304</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E92" s="2">
         <v>110004</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>57</v>
+      <c r="F92" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="4">
+      <c r="A93" s="3">
         <v>1305</v>
       </c>
-      <c r="B93" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E93" s="5">
+      <c r="B93" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="4">
         <v>110005</v>
       </c>
-      <c r="F93" s="6" t="s">
-        <v>57</v>
+      <c r="F93" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3195,19 +3262,19 @@
         <v>1306</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E94">
         <v>110006</v>
       </c>
-      <c r="F94" t="s">
-        <v>57</v>
+      <c r="F94" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3215,19 +3282,19 @@
         <v>1307</v>
       </c>
       <c r="B95" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D95" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E95">
         <v>110007</v>
       </c>
-      <c r="F95" t="s">
-        <v>57</v>
+      <c r="F95" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -3235,39 +3302,39 @@
         <v>1401</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="D96" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E96" s="2">
         <v>111001</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>58</v>
+      <c r="F96" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="4">
+      <c r="A97" s="3">
         <v>1402</v>
       </c>
-      <c r="B97" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E97" s="5">
+      <c r="B97" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="4">
         <v>111002</v>
       </c>
-      <c r="F97" s="6" t="s">
-        <v>58</v>
+      <c r="F97" s="2" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3275,99 +3342,99 @@
         <v>1403</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E98" s="2">
         <v>111003</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>58</v>
+      <c r="F98" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="4">
+      <c r="A99" s="3">
         <v>1404</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="4">
+        <v>111004</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="6">
+        <v>1405</v>
+      </c>
+      <c r="B100" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="C100" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E99" s="5">
-        <v>111004</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="7">
-        <v>1405</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E100" s="8">
+      <c r="D100" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="7">
         <v>111005</v>
       </c>
-      <c r="F100" s="9" t="s">
-        <v>58</v>
+      <c r="F100" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="7">
+      <c r="A101" s="6">
         <v>1406</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="7">
+        <v>111006</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="6">
+        <v>1407</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C101" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D101" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E101" s="8">
-        <v>111006</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="7">
-        <v>1407</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E102" s="8">
+      <c r="D102" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="7">
         <v>111007</v>
       </c>
-      <c r="F102" s="9" t="s">
-        <v>58</v>
+      <c r="F102" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -3375,19 +3442,19 @@
         <v>1501</v>
       </c>
       <c r="B103" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C103" t="s">
-        <v>103</v>
-      </c>
-      <c r="D103" s="8" t="s">
-        <v>36</v>
+        <v>100</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E103">
         <v>113001</v>
       </c>
       <c r="F103" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -3395,19 +3462,19 @@
         <v>1502</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C104" t="s">
-        <v>105</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>36</v>
+        <v>102</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E104">
         <v>113002</v>
       </c>
       <c r="F104" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -3415,19 +3482,19 @@
         <v>1503</v>
       </c>
       <c r="B105" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>107</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>36</v>
+        <v>104</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E105">
         <v>113003</v>
       </c>
       <c r="F105" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -3435,19 +3502,19 @@
         <v>1504</v>
       </c>
       <c r="B106" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C106" t="s">
-        <v>109</v>
-      </c>
-      <c r="D106" s="8" t="s">
-        <v>36</v>
+        <v>106</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E106">
         <v>113004</v>
       </c>
       <c r="F106" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -3455,19 +3522,19 @@
         <v>1505</v>
       </c>
       <c r="B107" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>111</v>
-      </c>
-      <c r="D107" s="8" t="s">
-        <v>36</v>
+        <v>108</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E107">
         <v>113005</v>
       </c>
       <c r="F107" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -3475,19 +3542,19 @@
         <v>1506</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C108" t="s">
-        <v>113</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>36</v>
+        <v>110</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E108">
         <v>113006</v>
       </c>
       <c r="F108" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -3495,19 +3562,19 @@
         <v>1507</v>
       </c>
       <c r="B109" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
-      </c>
-      <c r="D109" s="8" t="s">
-        <v>36</v>
+        <v>112</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="E109">
         <v>113007</v>
       </c>
       <c r="F109" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
